--- a/app/public/templates/programmes-template.xlsx
+++ b/app/public/templates/programmes-template.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -511,51 +511,58 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Optional, as in the WABYS curriculum manual: Domain K (knowledge), S (skill) or A (attitude); Year 1–3; Target level L1–L4 for skills; Core attitude A1–A7 for attitudes. The full manual is in wabys-curricula-2026.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>طريقة العمل</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>لكل تخصص شجرة مهارات: وحدة ← عنصر ← معيار أداء. سطر واحد لكل مهارة. السطر الذي يحتوي أعمدة التخصص فقط ينشئ التخصص أو يعدّل اسمه. اكتب المستوى الأعلى قبل ما تحته، واترك "رمز المستوى الأعلى" فارغًا للوحدة. اختر "Yes" في السلامة الحرجة للمهارة التي يمنع الرسوب فيها المتدرب من الاستمرار.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>PLMB | Plumbing | السباكة</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>PLMB | PLMB-U01 | Unit | Install water supply pipework | تركيب شبكات تغذية المياه | No | 40</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>PLMB | PLMB-U01-E1 | Element | PLMB-U01 | Cut and join copper pipe | قطع ووصل المواسير النحاس | No | 12</t>
+          <t>PLMB | PLMB-Y1-S | Unit | Year 1 · Practical skills | السنة الأولى · المهارات العملية | No | S | 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PLMB | PLMB-U01-E1-PC1 | Criterion | PLMB-U01-E1 | Uses the blowtorch safely | يستخدم لمبة اللحام بأمان | Yes</t>
+          <t>PLMB | PLMB-Y1-S-01 | Element | PLMB-Y1-S | Cut and join copper pipe | قطع ووصل المواسير النحاس | No | 12 | S | 1 | L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>PLMB | PLMB-Y1-S-01.1 | Criterion | PLMB-Y1-S-01 | Uses the blowtorch safely | يستخدم لمبة اللحام بأمان | Yes | S | 1</t>
         </is>
       </c>
     </row>
@@ -570,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J501"/>
+  <dimension ref="A1:N501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -583,6 +590,10 @@
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -646,6 +657,30 @@
 الساعات</t>
         </is>
       </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Domain (K/S/A)
+المجال (معرفة/مهارة/اتجاه)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Year
+السنة</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Target level
+مستوى الأداء المستهدف</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Core attitude
+الاتجاه الأساسي</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n"/>
@@ -658,6 +693,10 @@
       <c r="H2" s="6" t="n"/>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -670,6 +709,10 @@
       <c r="H3" s="6" t="n"/>
       <c r="I3" s="6" t="n"/>
       <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -682,6 +725,10 @@
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -694,6 +741,10 @@
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -706,6 +757,10 @@
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -718,6 +773,10 @@
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -730,6 +789,10 @@
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -742,6 +805,10 @@
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -754,6 +821,10 @@
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -766,6 +837,10 @@
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -778,6 +853,10 @@
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -790,6 +869,10 @@
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -802,6 +885,10 @@
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -814,6 +901,10 @@
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -826,6 +917,10 @@
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -838,6 +933,10 @@
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -850,6 +949,10 @@
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -862,6 +965,10 @@
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -874,6 +981,10 @@
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -886,6 +997,10 @@
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -898,6 +1013,10 @@
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -910,6 +1029,10 @@
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -922,6 +1045,10 @@
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -934,6 +1061,10 @@
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -946,6 +1077,10 @@
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -958,6 +1093,10 @@
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -970,6 +1109,10 @@
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -982,6 +1125,10 @@
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -994,6 +1141,10 @@
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1006,6 +1157,10 @@
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1018,6 +1173,10 @@
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1030,6 +1189,10 @@
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1042,6 +1205,10 @@
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1054,6 +1221,10 @@
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1066,6 +1237,10 @@
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1078,6 +1253,10 @@
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1090,6 +1269,10 @@
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1102,6 +1285,10 @@
       <c r="H39" s="6" t="n"/>
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1114,6 +1301,10 @@
       <c r="H40" s="6" t="n"/>
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1126,6 +1317,10 @@
       <c r="H41" s="6" t="n"/>
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1138,6 +1333,10 @@
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1150,6 +1349,10 @@
       <c r="H43" s="6" t="n"/>
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1162,6 +1365,10 @@
       <c r="H44" s="6" t="n"/>
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1174,6 +1381,10 @@
       <c r="H45" s="6" t="n"/>
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1186,6 +1397,10 @@
       <c r="H46" s="6" t="n"/>
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1198,6 +1413,10 @@
       <c r="H47" s="6" t="n"/>
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -1210,6 +1429,10 @@
       <c r="H48" s="6" t="n"/>
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
+      <c r="N48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1222,6 +1445,10 @@
       <c r="H49" s="6" t="n"/>
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -1234,6 +1461,10 @@
       <c r="H50" s="6" t="n"/>
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
+      <c r="N50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1246,6 +1477,10 @@
       <c r="H51" s="6" t="n"/>
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -1258,6 +1493,10 @@
       <c r="H52" s="6" t="n"/>
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1270,6 +1509,10 @@
       <c r="H53" s="6" t="n"/>
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -1282,6 +1525,10 @@
       <c r="H54" s="6" t="n"/>
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
+      <c r="N54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1294,6 +1541,10 @@
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="n"/>
+      <c r="M55" s="6" t="n"/>
+      <c r="N55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -1306,6 +1557,10 @@
       <c r="H56" s="6" t="n"/>
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
+      <c r="N56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1318,6 +1573,10 @@
       <c r="H57" s="6" t="n"/>
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="n"/>
+      <c r="M57" s="6" t="n"/>
+      <c r="N57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -1330,6 +1589,10 @@
       <c r="H58" s="6" t="n"/>
       <c r="I58" s="6" t="n"/>
       <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
+      <c r="N58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1342,6 +1605,10 @@
       <c r="H59" s="6" t="n"/>
       <c r="I59" s="6" t="n"/>
       <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
+      <c r="N59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -1354,6 +1621,10 @@
       <c r="H60" s="6" t="n"/>
       <c r="I60" s="6" t="n"/>
       <c r="J60" s="6" t="n"/>
+      <c r="K60" s="6" t="n"/>
+      <c r="L60" s="6" t="n"/>
+      <c r="M60" s="6" t="n"/>
+      <c r="N60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -1366,6 +1637,10 @@
       <c r="H61" s="6" t="n"/>
       <c r="I61" s="6" t="n"/>
       <c r="J61" s="6" t="n"/>
+      <c r="K61" s="6" t="n"/>
+      <c r="L61" s="6" t="n"/>
+      <c r="M61" s="6" t="n"/>
+      <c r="N61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -1378,6 +1653,10 @@
       <c r="H62" s="6" t="n"/>
       <c r="I62" s="6" t="n"/>
       <c r="J62" s="6" t="n"/>
+      <c r="K62" s="6" t="n"/>
+      <c r="L62" s="6" t="n"/>
+      <c r="M62" s="6" t="n"/>
+      <c r="N62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -1390,6 +1669,10 @@
       <c r="H63" s="6" t="n"/>
       <c r="I63" s="6" t="n"/>
       <c r="J63" s="6" t="n"/>
+      <c r="K63" s="6" t="n"/>
+      <c r="L63" s="6" t="n"/>
+      <c r="M63" s="6" t="n"/>
+      <c r="N63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -1402,6 +1685,10 @@
       <c r="H64" s="6" t="n"/>
       <c r="I64" s="6" t="n"/>
       <c r="J64" s="6" t="n"/>
+      <c r="K64" s="6" t="n"/>
+      <c r="L64" s="6" t="n"/>
+      <c r="M64" s="6" t="n"/>
+      <c r="N64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -1414,6 +1701,10 @@
       <c r="H65" s="6" t="n"/>
       <c r="I65" s="6" t="n"/>
       <c r="J65" s="6" t="n"/>
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="6" t="n"/>
+      <c r="M65" s="6" t="n"/>
+      <c r="N65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -1426,6 +1717,10 @@
       <c r="H66" s="6" t="n"/>
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="6" t="n"/>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="n"/>
+      <c r="M66" s="6" t="n"/>
+      <c r="N66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -1438,6 +1733,10 @@
       <c r="H67" s="6" t="n"/>
       <c r="I67" s="6" t="n"/>
       <c r="J67" s="6" t="n"/>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="n"/>
+      <c r="M67" s="6" t="n"/>
+      <c r="N67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -1450,6 +1749,10 @@
       <c r="H68" s="6" t="n"/>
       <c r="I68" s="6" t="n"/>
       <c r="J68" s="6" t="n"/>
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="6" t="n"/>
+      <c r="M68" s="6" t="n"/>
+      <c r="N68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -1462,6 +1765,10 @@
       <c r="H69" s="6" t="n"/>
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="6" t="n"/>
+      <c r="K69" s="6" t="n"/>
+      <c r="L69" s="6" t="n"/>
+      <c r="M69" s="6" t="n"/>
+      <c r="N69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -1474,6 +1781,10 @@
       <c r="H70" s="6" t="n"/>
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="6" t="n"/>
+      <c r="K70" s="6" t="n"/>
+      <c r="L70" s="6" t="n"/>
+      <c r="M70" s="6" t="n"/>
+      <c r="N70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -1486,6 +1797,10 @@
       <c r="H71" s="6" t="n"/>
       <c r="I71" s="6" t="n"/>
       <c r="J71" s="6" t="n"/>
+      <c r="K71" s="6" t="n"/>
+      <c r="L71" s="6" t="n"/>
+      <c r="M71" s="6" t="n"/>
+      <c r="N71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -1498,6 +1813,10 @@
       <c r="H72" s="6" t="n"/>
       <c r="I72" s="6" t="n"/>
       <c r="J72" s="6" t="n"/>
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="6" t="n"/>
+      <c r="M72" s="6" t="n"/>
+      <c r="N72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -1510,6 +1829,10 @@
       <c r="H73" s="6" t="n"/>
       <c r="I73" s="6" t="n"/>
       <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="6" t="n"/>
+      <c r="M73" s="6" t="n"/>
+      <c r="N73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
@@ -1522,6 +1845,10 @@
       <c r="H74" s="6" t="n"/>
       <c r="I74" s="6" t="n"/>
       <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="n"/>
+      <c r="M74" s="6" t="n"/>
+      <c r="N74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -1534,6 +1861,10 @@
       <c r="H75" s="6" t="n"/>
       <c r="I75" s="6" t="n"/>
       <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="n"/>
+      <c r="M75" s="6" t="n"/>
+      <c r="N75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -1546,6 +1877,10 @@
       <c r="H76" s="6" t="n"/>
       <c r="I76" s="6" t="n"/>
       <c r="J76" s="6" t="n"/>
+      <c r="K76" s="6" t="n"/>
+      <c r="L76" s="6" t="n"/>
+      <c r="M76" s="6" t="n"/>
+      <c r="N76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -1558,6 +1893,10 @@
       <c r="H77" s="6" t="n"/>
       <c r="I77" s="6" t="n"/>
       <c r="J77" s="6" t="n"/>
+      <c r="K77" s="6" t="n"/>
+      <c r="L77" s="6" t="n"/>
+      <c r="M77" s="6" t="n"/>
+      <c r="N77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
@@ -1570,6 +1909,10 @@
       <c r="H78" s="6" t="n"/>
       <c r="I78" s="6" t="n"/>
       <c r="J78" s="6" t="n"/>
+      <c r="K78" s="6" t="n"/>
+      <c r="L78" s="6" t="n"/>
+      <c r="M78" s="6" t="n"/>
+      <c r="N78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -1582,6 +1925,10 @@
       <c r="H79" s="6" t="n"/>
       <c r="I79" s="6" t="n"/>
       <c r="J79" s="6" t="n"/>
+      <c r="K79" s="6" t="n"/>
+      <c r="L79" s="6" t="n"/>
+      <c r="M79" s="6" t="n"/>
+      <c r="N79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -1594,6 +1941,10 @@
       <c r="H80" s="6" t="n"/>
       <c r="I80" s="6" t="n"/>
       <c r="J80" s="6" t="n"/>
+      <c r="K80" s="6" t="n"/>
+      <c r="L80" s="6" t="n"/>
+      <c r="M80" s="6" t="n"/>
+      <c r="N80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -1606,6 +1957,10 @@
       <c r="H81" s="6" t="n"/>
       <c r="I81" s="6" t="n"/>
       <c r="J81" s="6" t="n"/>
+      <c r="K81" s="6" t="n"/>
+      <c r="L81" s="6" t="n"/>
+      <c r="M81" s="6" t="n"/>
+      <c r="N81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
@@ -1618,6 +1973,10 @@
       <c r="H82" s="6" t="n"/>
       <c r="I82" s="6" t="n"/>
       <c r="J82" s="6" t="n"/>
+      <c r="K82" s="6" t="n"/>
+      <c r="L82" s="6" t="n"/>
+      <c r="M82" s="6" t="n"/>
+      <c r="N82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -1630,6 +1989,10 @@
       <c r="H83" s="6" t="n"/>
       <c r="I83" s="6" t="n"/>
       <c r="J83" s="6" t="n"/>
+      <c r="K83" s="6" t="n"/>
+      <c r="L83" s="6" t="n"/>
+      <c r="M83" s="6" t="n"/>
+      <c r="N83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -1642,6 +2005,10 @@
       <c r="H84" s="6" t="n"/>
       <c r="I84" s="6" t="n"/>
       <c r="J84" s="6" t="n"/>
+      <c r="K84" s="6" t="n"/>
+      <c r="L84" s="6" t="n"/>
+      <c r="M84" s="6" t="n"/>
+      <c r="N84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -1654,6 +2021,10 @@
       <c r="H85" s="6" t="n"/>
       <c r="I85" s="6" t="n"/>
       <c r="J85" s="6" t="n"/>
+      <c r="K85" s="6" t="n"/>
+      <c r="L85" s="6" t="n"/>
+      <c r="M85" s="6" t="n"/>
+      <c r="N85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
@@ -1666,6 +2037,10 @@
       <c r="H86" s="6" t="n"/>
       <c r="I86" s="6" t="n"/>
       <c r="J86" s="6" t="n"/>
+      <c r="K86" s="6" t="n"/>
+      <c r="L86" s="6" t="n"/>
+      <c r="M86" s="6" t="n"/>
+      <c r="N86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -1678,6 +2053,10 @@
       <c r="H87" s="6" t="n"/>
       <c r="I87" s="6" t="n"/>
       <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
+      <c r="L87" s="6" t="n"/>
+      <c r="M87" s="6" t="n"/>
+      <c r="N87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
@@ -1690,6 +2069,10 @@
       <c r="H88" s="6" t="n"/>
       <c r="I88" s="6" t="n"/>
       <c r="J88" s="6" t="n"/>
+      <c r="K88" s="6" t="n"/>
+      <c r="L88" s="6" t="n"/>
+      <c r="M88" s="6" t="n"/>
+      <c r="N88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -1702,6 +2085,10 @@
       <c r="H89" s="6" t="n"/>
       <c r="I89" s="6" t="n"/>
       <c r="J89" s="6" t="n"/>
+      <c r="K89" s="6" t="n"/>
+      <c r="L89" s="6" t="n"/>
+      <c r="M89" s="6" t="n"/>
+      <c r="N89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
@@ -1714,6 +2101,10 @@
       <c r="H90" s="6" t="n"/>
       <c r="I90" s="6" t="n"/>
       <c r="J90" s="6" t="n"/>
+      <c r="K90" s="6" t="n"/>
+      <c r="L90" s="6" t="n"/>
+      <c r="M90" s="6" t="n"/>
+      <c r="N90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -1726,6 +2117,10 @@
       <c r="H91" s="6" t="n"/>
       <c r="I91" s="6" t="n"/>
       <c r="J91" s="6" t="n"/>
+      <c r="K91" s="6" t="n"/>
+      <c r="L91" s="6" t="n"/>
+      <c r="M91" s="6" t="n"/>
+      <c r="N91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -1738,6 +2133,10 @@
       <c r="H92" s="6" t="n"/>
       <c r="I92" s="6" t="n"/>
       <c r="J92" s="6" t="n"/>
+      <c r="K92" s="6" t="n"/>
+      <c r="L92" s="6" t="n"/>
+      <c r="M92" s="6" t="n"/>
+      <c r="N92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -1750,6 +2149,10 @@
       <c r="H93" s="6" t="n"/>
       <c r="I93" s="6" t="n"/>
       <c r="J93" s="6" t="n"/>
+      <c r="K93" s="6" t="n"/>
+      <c r="L93" s="6" t="n"/>
+      <c r="M93" s="6" t="n"/>
+      <c r="N93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -1762,6 +2165,10 @@
       <c r="H94" s="6" t="n"/>
       <c r="I94" s="6" t="n"/>
       <c r="J94" s="6" t="n"/>
+      <c r="K94" s="6" t="n"/>
+      <c r="L94" s="6" t="n"/>
+      <c r="M94" s="6" t="n"/>
+      <c r="N94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -1774,6 +2181,10 @@
       <c r="H95" s="6" t="n"/>
       <c r="I95" s="6" t="n"/>
       <c r="J95" s="6" t="n"/>
+      <c r="K95" s="6" t="n"/>
+      <c r="L95" s="6" t="n"/>
+      <c r="M95" s="6" t="n"/>
+      <c r="N95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -1786,6 +2197,10 @@
       <c r="H96" s="6" t="n"/>
       <c r="I96" s="6" t="n"/>
       <c r="J96" s="6" t="n"/>
+      <c r="K96" s="6" t="n"/>
+      <c r="L96" s="6" t="n"/>
+      <c r="M96" s="6" t="n"/>
+      <c r="N96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -1798,6 +2213,10 @@
       <c r="H97" s="6" t="n"/>
       <c r="I97" s="6" t="n"/>
       <c r="J97" s="6" t="n"/>
+      <c r="K97" s="6" t="n"/>
+      <c r="L97" s="6" t="n"/>
+      <c r="M97" s="6" t="n"/>
+      <c r="N97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -1810,6 +2229,10 @@
       <c r="H98" s="6" t="n"/>
       <c r="I98" s="6" t="n"/>
       <c r="J98" s="6" t="n"/>
+      <c r="K98" s="6" t="n"/>
+      <c r="L98" s="6" t="n"/>
+      <c r="M98" s="6" t="n"/>
+      <c r="N98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -1822,6 +2245,10 @@
       <c r="H99" s="6" t="n"/>
       <c r="I99" s="6" t="n"/>
       <c r="J99" s="6" t="n"/>
+      <c r="K99" s="6" t="n"/>
+      <c r="L99" s="6" t="n"/>
+      <c r="M99" s="6" t="n"/>
+      <c r="N99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -1834,6 +2261,10 @@
       <c r="H100" s="6" t="n"/>
       <c r="I100" s="6" t="n"/>
       <c r="J100" s="6" t="n"/>
+      <c r="K100" s="6" t="n"/>
+      <c r="L100" s="6" t="n"/>
+      <c r="M100" s="6" t="n"/>
+      <c r="N100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -1846,6 +2277,10 @@
       <c r="H101" s="6" t="n"/>
       <c r="I101" s="6" t="n"/>
       <c r="J101" s="6" t="n"/>
+      <c r="K101" s="6" t="n"/>
+      <c r="L101" s="6" t="n"/>
+      <c r="M101" s="6" t="n"/>
+      <c r="N101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -1858,6 +2293,10 @@
       <c r="H102" s="6" t="n"/>
       <c r="I102" s="6" t="n"/>
       <c r="J102" s="6" t="n"/>
+      <c r="K102" s="6" t="n"/>
+      <c r="L102" s="6" t="n"/>
+      <c r="M102" s="6" t="n"/>
+      <c r="N102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -1870,6 +2309,10 @@
       <c r="H103" s="6" t="n"/>
       <c r="I103" s="6" t="n"/>
       <c r="J103" s="6" t="n"/>
+      <c r="K103" s="6" t="n"/>
+      <c r="L103" s="6" t="n"/>
+      <c r="M103" s="6" t="n"/>
+      <c r="N103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -1882,6 +2325,10 @@
       <c r="H104" s="6" t="n"/>
       <c r="I104" s="6" t="n"/>
       <c r="J104" s="6" t="n"/>
+      <c r="K104" s="6" t="n"/>
+      <c r="L104" s="6" t="n"/>
+      <c r="M104" s="6" t="n"/>
+      <c r="N104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -1894,6 +2341,10 @@
       <c r="H105" s="6" t="n"/>
       <c r="I105" s="6" t="n"/>
       <c r="J105" s="6" t="n"/>
+      <c r="K105" s="6" t="n"/>
+      <c r="L105" s="6" t="n"/>
+      <c r="M105" s="6" t="n"/>
+      <c r="N105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -1906,6 +2357,10 @@
       <c r="H106" s="6" t="n"/>
       <c r="I106" s="6" t="n"/>
       <c r="J106" s="6" t="n"/>
+      <c r="K106" s="6" t="n"/>
+      <c r="L106" s="6" t="n"/>
+      <c r="M106" s="6" t="n"/>
+      <c r="N106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -1918,6 +2373,10 @@
       <c r="H107" s="6" t="n"/>
       <c r="I107" s="6" t="n"/>
       <c r="J107" s="6" t="n"/>
+      <c r="K107" s="6" t="n"/>
+      <c r="L107" s="6" t="n"/>
+      <c r="M107" s="6" t="n"/>
+      <c r="N107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -1930,6 +2389,10 @@
       <c r="H108" s="6" t="n"/>
       <c r="I108" s="6" t="n"/>
       <c r="J108" s="6" t="n"/>
+      <c r="K108" s="6" t="n"/>
+      <c r="L108" s="6" t="n"/>
+      <c r="M108" s="6" t="n"/>
+      <c r="N108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
@@ -1942,6 +2405,10 @@
       <c r="H109" s="6" t="n"/>
       <c r="I109" s="6" t="n"/>
       <c r="J109" s="6" t="n"/>
+      <c r="K109" s="6" t="n"/>
+      <c r="L109" s="6" t="n"/>
+      <c r="M109" s="6" t="n"/>
+      <c r="N109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
@@ -1954,6 +2421,10 @@
       <c r="H110" s="6" t="n"/>
       <c r="I110" s="6" t="n"/>
       <c r="J110" s="6" t="n"/>
+      <c r="K110" s="6" t="n"/>
+      <c r="L110" s="6" t="n"/>
+      <c r="M110" s="6" t="n"/>
+      <c r="N110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
@@ -1966,6 +2437,10 @@
       <c r="H111" s="6" t="n"/>
       <c r="I111" s="6" t="n"/>
       <c r="J111" s="6" t="n"/>
+      <c r="K111" s="6" t="n"/>
+      <c r="L111" s="6" t="n"/>
+      <c r="M111" s="6" t="n"/>
+      <c r="N111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
@@ -1978,6 +2453,10 @@
       <c r="H112" s="6" t="n"/>
       <c r="I112" s="6" t="n"/>
       <c r="J112" s="6" t="n"/>
+      <c r="K112" s="6" t="n"/>
+      <c r="L112" s="6" t="n"/>
+      <c r="M112" s="6" t="n"/>
+      <c r="N112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
@@ -1990,6 +2469,10 @@
       <c r="H113" s="6" t="n"/>
       <c r="I113" s="6" t="n"/>
       <c r="J113" s="6" t="n"/>
+      <c r="K113" s="6" t="n"/>
+      <c r="L113" s="6" t="n"/>
+      <c r="M113" s="6" t="n"/>
+      <c r="N113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
@@ -2002,6 +2485,10 @@
       <c r="H114" s="6" t="n"/>
       <c r="I114" s="6" t="n"/>
       <c r="J114" s="6" t="n"/>
+      <c r="K114" s="6" t="n"/>
+      <c r="L114" s="6" t="n"/>
+      <c r="M114" s="6" t="n"/>
+      <c r="N114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
@@ -2014,6 +2501,10 @@
       <c r="H115" s="6" t="n"/>
       <c r="I115" s="6" t="n"/>
       <c r="J115" s="6" t="n"/>
+      <c r="K115" s="6" t="n"/>
+      <c r="L115" s="6" t="n"/>
+      <c r="M115" s="6" t="n"/>
+      <c r="N115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
@@ -2026,6 +2517,10 @@
       <c r="H116" s="6" t="n"/>
       <c r="I116" s="6" t="n"/>
       <c r="J116" s="6" t="n"/>
+      <c r="K116" s="6" t="n"/>
+      <c r="L116" s="6" t="n"/>
+      <c r="M116" s="6" t="n"/>
+      <c r="N116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -2038,6 +2533,10 @@
       <c r="H117" s="6" t="n"/>
       <c r="I117" s="6" t="n"/>
       <c r="J117" s="6" t="n"/>
+      <c r="K117" s="6" t="n"/>
+      <c r="L117" s="6" t="n"/>
+      <c r="M117" s="6" t="n"/>
+      <c r="N117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
@@ -2050,6 +2549,10 @@
       <c r="H118" s="6" t="n"/>
       <c r="I118" s="6" t="n"/>
       <c r="J118" s="6" t="n"/>
+      <c r="K118" s="6" t="n"/>
+      <c r="L118" s="6" t="n"/>
+      <c r="M118" s="6" t="n"/>
+      <c r="N118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
@@ -2062,6 +2565,10 @@
       <c r="H119" s="6" t="n"/>
       <c r="I119" s="6" t="n"/>
       <c r="J119" s="6" t="n"/>
+      <c r="K119" s="6" t="n"/>
+      <c r="L119" s="6" t="n"/>
+      <c r="M119" s="6" t="n"/>
+      <c r="N119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
@@ -2074,6 +2581,10 @@
       <c r="H120" s="6" t="n"/>
       <c r="I120" s="6" t="n"/>
       <c r="J120" s="6" t="n"/>
+      <c r="K120" s="6" t="n"/>
+      <c r="L120" s="6" t="n"/>
+      <c r="M120" s="6" t="n"/>
+      <c r="N120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
@@ -2086,6 +2597,10 @@
       <c r="H121" s="6" t="n"/>
       <c r="I121" s="6" t="n"/>
       <c r="J121" s="6" t="n"/>
+      <c r="K121" s="6" t="n"/>
+      <c r="L121" s="6" t="n"/>
+      <c r="M121" s="6" t="n"/>
+      <c r="N121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
@@ -2098,6 +2613,10 @@
       <c r="H122" s="6" t="n"/>
       <c r="I122" s="6" t="n"/>
       <c r="J122" s="6" t="n"/>
+      <c r="K122" s="6" t="n"/>
+      <c r="L122" s="6" t="n"/>
+      <c r="M122" s="6" t="n"/>
+      <c r="N122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
@@ -2110,6 +2629,10 @@
       <c r="H123" s="6" t="n"/>
       <c r="I123" s="6" t="n"/>
       <c r="J123" s="6" t="n"/>
+      <c r="K123" s="6" t="n"/>
+      <c r="L123" s="6" t="n"/>
+      <c r="M123" s="6" t="n"/>
+      <c r="N123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
@@ -2122,6 +2645,10 @@
       <c r="H124" s="6" t="n"/>
       <c r="I124" s="6" t="n"/>
       <c r="J124" s="6" t="n"/>
+      <c r="K124" s="6" t="n"/>
+      <c r="L124" s="6" t="n"/>
+      <c r="M124" s="6" t="n"/>
+      <c r="N124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
@@ -2134,6 +2661,10 @@
       <c r="H125" s="6" t="n"/>
       <c r="I125" s="6" t="n"/>
       <c r="J125" s="6" t="n"/>
+      <c r="K125" s="6" t="n"/>
+      <c r="L125" s="6" t="n"/>
+      <c r="M125" s="6" t="n"/>
+      <c r="N125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
@@ -2146,6 +2677,10 @@
       <c r="H126" s="6" t="n"/>
       <c r="I126" s="6" t="n"/>
       <c r="J126" s="6" t="n"/>
+      <c r="K126" s="6" t="n"/>
+      <c r="L126" s="6" t="n"/>
+      <c r="M126" s="6" t="n"/>
+      <c r="N126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
@@ -2158,6 +2693,10 @@
       <c r="H127" s="6" t="n"/>
       <c r="I127" s="6" t="n"/>
       <c r="J127" s="6" t="n"/>
+      <c r="K127" s="6" t="n"/>
+      <c r="L127" s="6" t="n"/>
+      <c r="M127" s="6" t="n"/>
+      <c r="N127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
@@ -2170,6 +2709,10 @@
       <c r="H128" s="6" t="n"/>
       <c r="I128" s="6" t="n"/>
       <c r="J128" s="6" t="n"/>
+      <c r="K128" s="6" t="n"/>
+      <c r="L128" s="6" t="n"/>
+      <c r="M128" s="6" t="n"/>
+      <c r="N128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
@@ -2182,6 +2725,10 @@
       <c r="H129" s="6" t="n"/>
       <c r="I129" s="6" t="n"/>
       <c r="J129" s="6" t="n"/>
+      <c r="K129" s="6" t="n"/>
+      <c r="L129" s="6" t="n"/>
+      <c r="M129" s="6" t="n"/>
+      <c r="N129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
@@ -2194,6 +2741,10 @@
       <c r="H130" s="6" t="n"/>
       <c r="I130" s="6" t="n"/>
       <c r="J130" s="6" t="n"/>
+      <c r="K130" s="6" t="n"/>
+      <c r="L130" s="6" t="n"/>
+      <c r="M130" s="6" t="n"/>
+      <c r="N130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
@@ -2206,6 +2757,10 @@
       <c r="H131" s="6" t="n"/>
       <c r="I131" s="6" t="n"/>
       <c r="J131" s="6" t="n"/>
+      <c r="K131" s="6" t="n"/>
+      <c r="L131" s="6" t="n"/>
+      <c r="M131" s="6" t="n"/>
+      <c r="N131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
@@ -2218,6 +2773,10 @@
       <c r="H132" s="6" t="n"/>
       <c r="I132" s="6" t="n"/>
       <c r="J132" s="6" t="n"/>
+      <c r="K132" s="6" t="n"/>
+      <c r="L132" s="6" t="n"/>
+      <c r="M132" s="6" t="n"/>
+      <c r="N132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
@@ -2230,6 +2789,10 @@
       <c r="H133" s="6" t="n"/>
       <c r="I133" s="6" t="n"/>
       <c r="J133" s="6" t="n"/>
+      <c r="K133" s="6" t="n"/>
+      <c r="L133" s="6" t="n"/>
+      <c r="M133" s="6" t="n"/>
+      <c r="N133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
@@ -2242,6 +2805,10 @@
       <c r="H134" s="6" t="n"/>
       <c r="I134" s="6" t="n"/>
       <c r="J134" s="6" t="n"/>
+      <c r="K134" s="6" t="n"/>
+      <c r="L134" s="6" t="n"/>
+      <c r="M134" s="6" t="n"/>
+      <c r="N134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
@@ -2254,6 +2821,10 @@
       <c r="H135" s="6" t="n"/>
       <c r="I135" s="6" t="n"/>
       <c r="J135" s="6" t="n"/>
+      <c r="K135" s="6" t="n"/>
+      <c r="L135" s="6" t="n"/>
+      <c r="M135" s="6" t="n"/>
+      <c r="N135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
@@ -2266,6 +2837,10 @@
       <c r="H136" s="6" t="n"/>
       <c r="I136" s="6" t="n"/>
       <c r="J136" s="6" t="n"/>
+      <c r="K136" s="6" t="n"/>
+      <c r="L136" s="6" t="n"/>
+      <c r="M136" s="6" t="n"/>
+      <c r="N136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
@@ -2278,6 +2853,10 @@
       <c r="H137" s="6" t="n"/>
       <c r="I137" s="6" t="n"/>
       <c r="J137" s="6" t="n"/>
+      <c r="K137" s="6" t="n"/>
+      <c r="L137" s="6" t="n"/>
+      <c r="M137" s="6" t="n"/>
+      <c r="N137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
@@ -2290,6 +2869,10 @@
       <c r="H138" s="6" t="n"/>
       <c r="I138" s="6" t="n"/>
       <c r="J138" s="6" t="n"/>
+      <c r="K138" s="6" t="n"/>
+      <c r="L138" s="6" t="n"/>
+      <c r="M138" s="6" t="n"/>
+      <c r="N138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
@@ -2302,6 +2885,10 @@
       <c r="H139" s="6" t="n"/>
       <c r="I139" s="6" t="n"/>
       <c r="J139" s="6" t="n"/>
+      <c r="K139" s="6" t="n"/>
+      <c r="L139" s="6" t="n"/>
+      <c r="M139" s="6" t="n"/>
+      <c r="N139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
@@ -2314,6 +2901,10 @@
       <c r="H140" s="6" t="n"/>
       <c r="I140" s="6" t="n"/>
       <c r="J140" s="6" t="n"/>
+      <c r="K140" s="6" t="n"/>
+      <c r="L140" s="6" t="n"/>
+      <c r="M140" s="6" t="n"/>
+      <c r="N140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
@@ -2326,6 +2917,10 @@
       <c r="H141" s="6" t="n"/>
       <c r="I141" s="6" t="n"/>
       <c r="J141" s="6" t="n"/>
+      <c r="K141" s="6" t="n"/>
+      <c r="L141" s="6" t="n"/>
+      <c r="M141" s="6" t="n"/>
+      <c r="N141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
@@ -2338,6 +2933,10 @@
       <c r="H142" s="6" t="n"/>
       <c r="I142" s="6" t="n"/>
       <c r="J142" s="6" t="n"/>
+      <c r="K142" s="6" t="n"/>
+      <c r="L142" s="6" t="n"/>
+      <c r="M142" s="6" t="n"/>
+      <c r="N142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
@@ -2350,6 +2949,10 @@
       <c r="H143" s="6" t="n"/>
       <c r="I143" s="6" t="n"/>
       <c r="J143" s="6" t="n"/>
+      <c r="K143" s="6" t="n"/>
+      <c r="L143" s="6" t="n"/>
+      <c r="M143" s="6" t="n"/>
+      <c r="N143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
@@ -2362,6 +2965,10 @@
       <c r="H144" s="6" t="n"/>
       <c r="I144" s="6" t="n"/>
       <c r="J144" s="6" t="n"/>
+      <c r="K144" s="6" t="n"/>
+      <c r="L144" s="6" t="n"/>
+      <c r="M144" s="6" t="n"/>
+      <c r="N144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
@@ -2374,6 +2981,10 @@
       <c r="H145" s="6" t="n"/>
       <c r="I145" s="6" t="n"/>
       <c r="J145" s="6" t="n"/>
+      <c r="K145" s="6" t="n"/>
+      <c r="L145" s="6" t="n"/>
+      <c r="M145" s="6" t="n"/>
+      <c r="N145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
@@ -2386,6 +2997,10 @@
       <c r="H146" s="6" t="n"/>
       <c r="I146" s="6" t="n"/>
       <c r="J146" s="6" t="n"/>
+      <c r="K146" s="6" t="n"/>
+      <c r="L146" s="6" t="n"/>
+      <c r="M146" s="6" t="n"/>
+      <c r="N146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
@@ -2398,6 +3013,10 @@
       <c r="H147" s="6" t="n"/>
       <c r="I147" s="6" t="n"/>
       <c r="J147" s="6" t="n"/>
+      <c r="K147" s="6" t="n"/>
+      <c r="L147" s="6" t="n"/>
+      <c r="M147" s="6" t="n"/>
+      <c r="N147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
@@ -2410,6 +3029,10 @@
       <c r="H148" s="6" t="n"/>
       <c r="I148" s="6" t="n"/>
       <c r="J148" s="6" t="n"/>
+      <c r="K148" s="6" t="n"/>
+      <c r="L148" s="6" t="n"/>
+      <c r="M148" s="6" t="n"/>
+      <c r="N148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
@@ -2422,6 +3045,10 @@
       <c r="H149" s="6" t="n"/>
       <c r="I149" s="6" t="n"/>
       <c r="J149" s="6" t="n"/>
+      <c r="K149" s="6" t="n"/>
+      <c r="L149" s="6" t="n"/>
+      <c r="M149" s="6" t="n"/>
+      <c r="N149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
@@ -2434,6 +3061,10 @@
       <c r="H150" s="6" t="n"/>
       <c r="I150" s="6" t="n"/>
       <c r="J150" s="6" t="n"/>
+      <c r="K150" s="6" t="n"/>
+      <c r="L150" s="6" t="n"/>
+      <c r="M150" s="6" t="n"/>
+      <c r="N150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n"/>
@@ -2446,6 +3077,10 @@
       <c r="H151" s="6" t="n"/>
       <c r="I151" s="6" t="n"/>
       <c r="J151" s="6" t="n"/>
+      <c r="K151" s="6" t="n"/>
+      <c r="L151" s="6" t="n"/>
+      <c r="M151" s="6" t="n"/>
+      <c r="N151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n"/>
@@ -2458,6 +3093,10 @@
       <c r="H152" s="6" t="n"/>
       <c r="I152" s="6" t="n"/>
       <c r="J152" s="6" t="n"/>
+      <c r="K152" s="6" t="n"/>
+      <c r="L152" s="6" t="n"/>
+      <c r="M152" s="6" t="n"/>
+      <c r="N152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n"/>
@@ -2470,6 +3109,10 @@
       <c r="H153" s="6" t="n"/>
       <c r="I153" s="6" t="n"/>
       <c r="J153" s="6" t="n"/>
+      <c r="K153" s="6" t="n"/>
+      <c r="L153" s="6" t="n"/>
+      <c r="M153" s="6" t="n"/>
+      <c r="N153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n"/>
@@ -2482,6 +3125,10 @@
       <c r="H154" s="6" t="n"/>
       <c r="I154" s="6" t="n"/>
       <c r="J154" s="6" t="n"/>
+      <c r="K154" s="6" t="n"/>
+      <c r="L154" s="6" t="n"/>
+      <c r="M154" s="6" t="n"/>
+      <c r="N154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n"/>
@@ -2494,6 +3141,10 @@
       <c r="H155" s="6" t="n"/>
       <c r="I155" s="6" t="n"/>
       <c r="J155" s="6" t="n"/>
+      <c r="K155" s="6" t="n"/>
+      <c r="L155" s="6" t="n"/>
+      <c r="M155" s="6" t="n"/>
+      <c r="N155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n"/>
@@ -2506,6 +3157,10 @@
       <c r="H156" s="6" t="n"/>
       <c r="I156" s="6" t="n"/>
       <c r="J156" s="6" t="n"/>
+      <c r="K156" s="6" t="n"/>
+      <c r="L156" s="6" t="n"/>
+      <c r="M156" s="6" t="n"/>
+      <c r="N156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n"/>
@@ -2518,6 +3173,10 @@
       <c r="H157" s="6" t="n"/>
       <c r="I157" s="6" t="n"/>
       <c r="J157" s="6" t="n"/>
+      <c r="K157" s="6" t="n"/>
+      <c r="L157" s="6" t="n"/>
+      <c r="M157" s="6" t="n"/>
+      <c r="N157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n"/>
@@ -2530,6 +3189,10 @@
       <c r="H158" s="6" t="n"/>
       <c r="I158" s="6" t="n"/>
       <c r="J158" s="6" t="n"/>
+      <c r="K158" s="6" t="n"/>
+      <c r="L158" s="6" t="n"/>
+      <c r="M158" s="6" t="n"/>
+      <c r="N158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n"/>
@@ -2542,6 +3205,10 @@
       <c r="H159" s="6" t="n"/>
       <c r="I159" s="6" t="n"/>
       <c r="J159" s="6" t="n"/>
+      <c r="K159" s="6" t="n"/>
+      <c r="L159" s="6" t="n"/>
+      <c r="M159" s="6" t="n"/>
+      <c r="N159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n"/>
@@ -2554,6 +3221,10 @@
       <c r="H160" s="6" t="n"/>
       <c r="I160" s="6" t="n"/>
       <c r="J160" s="6" t="n"/>
+      <c r="K160" s="6" t="n"/>
+      <c r="L160" s="6" t="n"/>
+      <c r="M160" s="6" t="n"/>
+      <c r="N160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n"/>
@@ -2566,6 +3237,10 @@
       <c r="H161" s="6" t="n"/>
       <c r="I161" s="6" t="n"/>
       <c r="J161" s="6" t="n"/>
+      <c r="K161" s="6" t="n"/>
+      <c r="L161" s="6" t="n"/>
+      <c r="M161" s="6" t="n"/>
+      <c r="N161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n"/>
@@ -2578,6 +3253,10 @@
       <c r="H162" s="6" t="n"/>
       <c r="I162" s="6" t="n"/>
       <c r="J162" s="6" t="n"/>
+      <c r="K162" s="6" t="n"/>
+      <c r="L162" s="6" t="n"/>
+      <c r="M162" s="6" t="n"/>
+      <c r="N162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n"/>
@@ -2590,6 +3269,10 @@
       <c r="H163" s="6" t="n"/>
       <c r="I163" s="6" t="n"/>
       <c r="J163" s="6" t="n"/>
+      <c r="K163" s="6" t="n"/>
+      <c r="L163" s="6" t="n"/>
+      <c r="M163" s="6" t="n"/>
+      <c r="N163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n"/>
@@ -2602,6 +3285,10 @@
       <c r="H164" s="6" t="n"/>
       <c r="I164" s="6" t="n"/>
       <c r="J164" s="6" t="n"/>
+      <c r="K164" s="6" t="n"/>
+      <c r="L164" s="6" t="n"/>
+      <c r="M164" s="6" t="n"/>
+      <c r="N164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n"/>
@@ -2614,6 +3301,10 @@
       <c r="H165" s="6" t="n"/>
       <c r="I165" s="6" t="n"/>
       <c r="J165" s="6" t="n"/>
+      <c r="K165" s="6" t="n"/>
+      <c r="L165" s="6" t="n"/>
+      <c r="M165" s="6" t="n"/>
+      <c r="N165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n"/>
@@ -2626,6 +3317,10 @@
       <c r="H166" s="6" t="n"/>
       <c r="I166" s="6" t="n"/>
       <c r="J166" s="6" t="n"/>
+      <c r="K166" s="6" t="n"/>
+      <c r="L166" s="6" t="n"/>
+      <c r="M166" s="6" t="n"/>
+      <c r="N166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n"/>
@@ -2638,6 +3333,10 @@
       <c r="H167" s="6" t="n"/>
       <c r="I167" s="6" t="n"/>
       <c r="J167" s="6" t="n"/>
+      <c r="K167" s="6" t="n"/>
+      <c r="L167" s="6" t="n"/>
+      <c r="M167" s="6" t="n"/>
+      <c r="N167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n"/>
@@ -2650,6 +3349,10 @@
       <c r="H168" s="6" t="n"/>
       <c r="I168" s="6" t="n"/>
       <c r="J168" s="6" t="n"/>
+      <c r="K168" s="6" t="n"/>
+      <c r="L168" s="6" t="n"/>
+      <c r="M168" s="6" t="n"/>
+      <c r="N168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n"/>
@@ -2662,6 +3365,10 @@
       <c r="H169" s="6" t="n"/>
       <c r="I169" s="6" t="n"/>
       <c r="J169" s="6" t="n"/>
+      <c r="K169" s="6" t="n"/>
+      <c r="L169" s="6" t="n"/>
+      <c r="M169" s="6" t="n"/>
+      <c r="N169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n"/>
@@ -2674,6 +3381,10 @@
       <c r="H170" s="6" t="n"/>
       <c r="I170" s="6" t="n"/>
       <c r="J170" s="6" t="n"/>
+      <c r="K170" s="6" t="n"/>
+      <c r="L170" s="6" t="n"/>
+      <c r="M170" s="6" t="n"/>
+      <c r="N170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n"/>
@@ -2686,6 +3397,10 @@
       <c r="H171" s="6" t="n"/>
       <c r="I171" s="6" t="n"/>
       <c r="J171" s="6" t="n"/>
+      <c r="K171" s="6" t="n"/>
+      <c r="L171" s="6" t="n"/>
+      <c r="M171" s="6" t="n"/>
+      <c r="N171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n"/>
@@ -2698,6 +3413,10 @@
       <c r="H172" s="6" t="n"/>
       <c r="I172" s="6" t="n"/>
       <c r="J172" s="6" t="n"/>
+      <c r="K172" s="6" t="n"/>
+      <c r="L172" s="6" t="n"/>
+      <c r="M172" s="6" t="n"/>
+      <c r="N172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n"/>
@@ -2710,6 +3429,10 @@
       <c r="H173" s="6" t="n"/>
       <c r="I173" s="6" t="n"/>
       <c r="J173" s="6" t="n"/>
+      <c r="K173" s="6" t="n"/>
+      <c r="L173" s="6" t="n"/>
+      <c r="M173" s="6" t="n"/>
+      <c r="N173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n"/>
@@ -2722,6 +3445,10 @@
       <c r="H174" s="6" t="n"/>
       <c r="I174" s="6" t="n"/>
       <c r="J174" s="6" t="n"/>
+      <c r="K174" s="6" t="n"/>
+      <c r="L174" s="6" t="n"/>
+      <c r="M174" s="6" t="n"/>
+      <c r="N174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n"/>
@@ -2734,6 +3461,10 @@
       <c r="H175" s="6" t="n"/>
       <c r="I175" s="6" t="n"/>
       <c r="J175" s="6" t="n"/>
+      <c r="K175" s="6" t="n"/>
+      <c r="L175" s="6" t="n"/>
+      <c r="M175" s="6" t="n"/>
+      <c r="N175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n"/>
@@ -2746,6 +3477,10 @@
       <c r="H176" s="6" t="n"/>
       <c r="I176" s="6" t="n"/>
       <c r="J176" s="6" t="n"/>
+      <c r="K176" s="6" t="n"/>
+      <c r="L176" s="6" t="n"/>
+      <c r="M176" s="6" t="n"/>
+      <c r="N176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n"/>
@@ -2758,6 +3493,10 @@
       <c r="H177" s="6" t="n"/>
       <c r="I177" s="6" t="n"/>
       <c r="J177" s="6" t="n"/>
+      <c r="K177" s="6" t="n"/>
+      <c r="L177" s="6" t="n"/>
+      <c r="M177" s="6" t="n"/>
+      <c r="N177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n"/>
@@ -2770,6 +3509,10 @@
       <c r="H178" s="6" t="n"/>
       <c r="I178" s="6" t="n"/>
       <c r="J178" s="6" t="n"/>
+      <c r="K178" s="6" t="n"/>
+      <c r="L178" s="6" t="n"/>
+      <c r="M178" s="6" t="n"/>
+      <c r="N178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n"/>
@@ -2782,6 +3525,10 @@
       <c r="H179" s="6" t="n"/>
       <c r="I179" s="6" t="n"/>
       <c r="J179" s="6" t="n"/>
+      <c r="K179" s="6" t="n"/>
+      <c r="L179" s="6" t="n"/>
+      <c r="M179" s="6" t="n"/>
+      <c r="N179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n"/>
@@ -2794,6 +3541,10 @@
       <c r="H180" s="6" t="n"/>
       <c r="I180" s="6" t="n"/>
       <c r="J180" s="6" t="n"/>
+      <c r="K180" s="6" t="n"/>
+      <c r="L180" s="6" t="n"/>
+      <c r="M180" s="6" t="n"/>
+      <c r="N180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n"/>
@@ -2806,6 +3557,10 @@
       <c r="H181" s="6" t="n"/>
       <c r="I181" s="6" t="n"/>
       <c r="J181" s="6" t="n"/>
+      <c r="K181" s="6" t="n"/>
+      <c r="L181" s="6" t="n"/>
+      <c r="M181" s="6" t="n"/>
+      <c r="N181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n"/>
@@ -2818,6 +3573,10 @@
       <c r="H182" s="6" t="n"/>
       <c r="I182" s="6" t="n"/>
       <c r="J182" s="6" t="n"/>
+      <c r="K182" s="6" t="n"/>
+      <c r="L182" s="6" t="n"/>
+      <c r="M182" s="6" t="n"/>
+      <c r="N182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n"/>
@@ -2830,6 +3589,10 @@
       <c r="H183" s="6" t="n"/>
       <c r="I183" s="6" t="n"/>
       <c r="J183" s="6" t="n"/>
+      <c r="K183" s="6" t="n"/>
+      <c r="L183" s="6" t="n"/>
+      <c r="M183" s="6" t="n"/>
+      <c r="N183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n"/>
@@ -2842,6 +3605,10 @@
       <c r="H184" s="6" t="n"/>
       <c r="I184" s="6" t="n"/>
       <c r="J184" s="6" t="n"/>
+      <c r="K184" s="6" t="n"/>
+      <c r="L184" s="6" t="n"/>
+      <c r="M184" s="6" t="n"/>
+      <c r="N184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n"/>
@@ -2854,6 +3621,10 @@
       <c r="H185" s="6" t="n"/>
       <c r="I185" s="6" t="n"/>
       <c r="J185" s="6" t="n"/>
+      <c r="K185" s="6" t="n"/>
+      <c r="L185" s="6" t="n"/>
+      <c r="M185" s="6" t="n"/>
+      <c r="N185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n"/>
@@ -2866,6 +3637,10 @@
       <c r="H186" s="6" t="n"/>
       <c r="I186" s="6" t="n"/>
       <c r="J186" s="6" t="n"/>
+      <c r="K186" s="6" t="n"/>
+      <c r="L186" s="6" t="n"/>
+      <c r="M186" s="6" t="n"/>
+      <c r="N186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n"/>
@@ -2878,6 +3653,10 @@
       <c r="H187" s="6" t="n"/>
       <c r="I187" s="6" t="n"/>
       <c r="J187" s="6" t="n"/>
+      <c r="K187" s="6" t="n"/>
+      <c r="L187" s="6" t="n"/>
+      <c r="M187" s="6" t="n"/>
+      <c r="N187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n"/>
@@ -2890,6 +3669,10 @@
       <c r="H188" s="6" t="n"/>
       <c r="I188" s="6" t="n"/>
       <c r="J188" s="6" t="n"/>
+      <c r="K188" s="6" t="n"/>
+      <c r="L188" s="6" t="n"/>
+      <c r="M188" s="6" t="n"/>
+      <c r="N188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n"/>
@@ -2902,6 +3685,10 @@
       <c r="H189" s="6" t="n"/>
       <c r="I189" s="6" t="n"/>
       <c r="J189" s="6" t="n"/>
+      <c r="K189" s="6" t="n"/>
+      <c r="L189" s="6" t="n"/>
+      <c r="M189" s="6" t="n"/>
+      <c r="N189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n"/>
@@ -2914,6 +3701,10 @@
       <c r="H190" s="6" t="n"/>
       <c r="I190" s="6" t="n"/>
       <c r="J190" s="6" t="n"/>
+      <c r="K190" s="6" t="n"/>
+      <c r="L190" s="6" t="n"/>
+      <c r="M190" s="6" t="n"/>
+      <c r="N190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n"/>
@@ -2926,6 +3717,10 @@
       <c r="H191" s="6" t="n"/>
       <c r="I191" s="6" t="n"/>
       <c r="J191" s="6" t="n"/>
+      <c r="K191" s="6" t="n"/>
+      <c r="L191" s="6" t="n"/>
+      <c r="M191" s="6" t="n"/>
+      <c r="N191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n"/>
@@ -2938,6 +3733,10 @@
       <c r="H192" s="6" t="n"/>
       <c r="I192" s="6" t="n"/>
       <c r="J192" s="6" t="n"/>
+      <c r="K192" s="6" t="n"/>
+      <c r="L192" s="6" t="n"/>
+      <c r="M192" s="6" t="n"/>
+      <c r="N192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n"/>
@@ -2950,6 +3749,10 @@
       <c r="H193" s="6" t="n"/>
       <c r="I193" s="6" t="n"/>
       <c r="J193" s="6" t="n"/>
+      <c r="K193" s="6" t="n"/>
+      <c r="L193" s="6" t="n"/>
+      <c r="M193" s="6" t="n"/>
+      <c r="N193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n"/>
@@ -2962,6 +3765,10 @@
       <c r="H194" s="6" t="n"/>
       <c r="I194" s="6" t="n"/>
       <c r="J194" s="6" t="n"/>
+      <c r="K194" s="6" t="n"/>
+      <c r="L194" s="6" t="n"/>
+      <c r="M194" s="6" t="n"/>
+      <c r="N194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n"/>
@@ -2974,6 +3781,10 @@
       <c r="H195" s="6" t="n"/>
       <c r="I195" s="6" t="n"/>
       <c r="J195" s="6" t="n"/>
+      <c r="K195" s="6" t="n"/>
+      <c r="L195" s="6" t="n"/>
+      <c r="M195" s="6" t="n"/>
+      <c r="N195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n"/>
@@ -2986,6 +3797,10 @@
       <c r="H196" s="6" t="n"/>
       <c r="I196" s="6" t="n"/>
       <c r="J196" s="6" t="n"/>
+      <c r="K196" s="6" t="n"/>
+      <c r="L196" s="6" t="n"/>
+      <c r="M196" s="6" t="n"/>
+      <c r="N196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n"/>
@@ -2998,6 +3813,10 @@
       <c r="H197" s="6" t="n"/>
       <c r="I197" s="6" t="n"/>
       <c r="J197" s="6" t="n"/>
+      <c r="K197" s="6" t="n"/>
+      <c r="L197" s="6" t="n"/>
+      <c r="M197" s="6" t="n"/>
+      <c r="N197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n"/>
@@ -3010,6 +3829,10 @@
       <c r="H198" s="6" t="n"/>
       <c r="I198" s="6" t="n"/>
       <c r="J198" s="6" t="n"/>
+      <c r="K198" s="6" t="n"/>
+      <c r="L198" s="6" t="n"/>
+      <c r="M198" s="6" t="n"/>
+      <c r="N198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n"/>
@@ -3022,6 +3845,10 @@
       <c r="H199" s="6" t="n"/>
       <c r="I199" s="6" t="n"/>
       <c r="J199" s="6" t="n"/>
+      <c r="K199" s="6" t="n"/>
+      <c r="L199" s="6" t="n"/>
+      <c r="M199" s="6" t="n"/>
+      <c r="N199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n"/>
@@ -3034,6 +3861,10 @@
       <c r="H200" s="6" t="n"/>
       <c r="I200" s="6" t="n"/>
       <c r="J200" s="6" t="n"/>
+      <c r="K200" s="6" t="n"/>
+      <c r="L200" s="6" t="n"/>
+      <c r="M200" s="6" t="n"/>
+      <c r="N200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n"/>
@@ -3046,6 +3877,10 @@
       <c r="H201" s="6" t="n"/>
       <c r="I201" s="6" t="n"/>
       <c r="J201" s="6" t="n"/>
+      <c r="K201" s="6" t="n"/>
+      <c r="L201" s="6" t="n"/>
+      <c r="M201" s="6" t="n"/>
+      <c r="N201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n"/>
@@ -3058,6 +3893,10 @@
       <c r="H202" s="6" t="n"/>
       <c r="I202" s="6" t="n"/>
       <c r="J202" s="6" t="n"/>
+      <c r="K202" s="6" t="n"/>
+      <c r="L202" s="6" t="n"/>
+      <c r="M202" s="6" t="n"/>
+      <c r="N202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n"/>
@@ -3070,6 +3909,10 @@
       <c r="H203" s="6" t="n"/>
       <c r="I203" s="6" t="n"/>
       <c r="J203" s="6" t="n"/>
+      <c r="K203" s="6" t="n"/>
+      <c r="L203" s="6" t="n"/>
+      <c r="M203" s="6" t="n"/>
+      <c r="N203" s="6" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n"/>
@@ -3082,6 +3925,10 @@
       <c r="H204" s="6" t="n"/>
       <c r="I204" s="6" t="n"/>
       <c r="J204" s="6" t="n"/>
+      <c r="K204" s="6" t="n"/>
+      <c r="L204" s="6" t="n"/>
+      <c r="M204" s="6" t="n"/>
+      <c r="N204" s="6" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="n"/>
@@ -3094,6 +3941,10 @@
       <c r="H205" s="6" t="n"/>
       <c r="I205" s="6" t="n"/>
       <c r="J205" s="6" t="n"/>
+      <c r="K205" s="6" t="n"/>
+      <c r="L205" s="6" t="n"/>
+      <c r="M205" s="6" t="n"/>
+      <c r="N205" s="6" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="n"/>
@@ -3106,6 +3957,10 @@
       <c r="H206" s="6" t="n"/>
       <c r="I206" s="6" t="n"/>
       <c r="J206" s="6" t="n"/>
+      <c r="K206" s="6" t="n"/>
+      <c r="L206" s="6" t="n"/>
+      <c r="M206" s="6" t="n"/>
+      <c r="N206" s="6" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="n"/>
@@ -3118,6 +3973,10 @@
       <c r="H207" s="6" t="n"/>
       <c r="I207" s="6" t="n"/>
       <c r="J207" s="6" t="n"/>
+      <c r="K207" s="6" t="n"/>
+      <c r="L207" s="6" t="n"/>
+      <c r="M207" s="6" t="n"/>
+      <c r="N207" s="6" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="n"/>
@@ -3130,6 +3989,10 @@
       <c r="H208" s="6" t="n"/>
       <c r="I208" s="6" t="n"/>
       <c r="J208" s="6" t="n"/>
+      <c r="K208" s="6" t="n"/>
+      <c r="L208" s="6" t="n"/>
+      <c r="M208" s="6" t="n"/>
+      <c r="N208" s="6" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="n"/>
@@ -3142,6 +4005,10 @@
       <c r="H209" s="6" t="n"/>
       <c r="I209" s="6" t="n"/>
       <c r="J209" s="6" t="n"/>
+      <c r="K209" s="6" t="n"/>
+      <c r="L209" s="6" t="n"/>
+      <c r="M209" s="6" t="n"/>
+      <c r="N209" s="6" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="n"/>
@@ -3154,6 +4021,10 @@
       <c r="H210" s="6" t="n"/>
       <c r="I210" s="6" t="n"/>
       <c r="J210" s="6" t="n"/>
+      <c r="K210" s="6" t="n"/>
+      <c r="L210" s="6" t="n"/>
+      <c r="M210" s="6" t="n"/>
+      <c r="N210" s="6" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="n"/>
@@ -3166,6 +4037,10 @@
       <c r="H211" s="6" t="n"/>
       <c r="I211" s="6" t="n"/>
       <c r="J211" s="6" t="n"/>
+      <c r="K211" s="6" t="n"/>
+      <c r="L211" s="6" t="n"/>
+      <c r="M211" s="6" t="n"/>
+      <c r="N211" s="6" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="n"/>
@@ -3178,6 +4053,10 @@
       <c r="H212" s="6" t="n"/>
       <c r="I212" s="6" t="n"/>
       <c r="J212" s="6" t="n"/>
+      <c r="K212" s="6" t="n"/>
+      <c r="L212" s="6" t="n"/>
+      <c r="M212" s="6" t="n"/>
+      <c r="N212" s="6" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="n"/>
@@ -3190,6 +4069,10 @@
       <c r="H213" s="6" t="n"/>
       <c r="I213" s="6" t="n"/>
       <c r="J213" s="6" t="n"/>
+      <c r="K213" s="6" t="n"/>
+      <c r="L213" s="6" t="n"/>
+      <c r="M213" s="6" t="n"/>
+      <c r="N213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="n"/>
@@ -3202,6 +4085,10 @@
       <c r="H214" s="6" t="n"/>
       <c r="I214" s="6" t="n"/>
       <c r="J214" s="6" t="n"/>
+      <c r="K214" s="6" t="n"/>
+      <c r="L214" s="6" t="n"/>
+      <c r="M214" s="6" t="n"/>
+      <c r="N214" s="6" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="n"/>
@@ -3214,6 +4101,10 @@
       <c r="H215" s="6" t="n"/>
       <c r="I215" s="6" t="n"/>
       <c r="J215" s="6" t="n"/>
+      <c r="K215" s="6" t="n"/>
+      <c r="L215" s="6" t="n"/>
+      <c r="M215" s="6" t="n"/>
+      <c r="N215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="n"/>
@@ -3226,6 +4117,10 @@
       <c r="H216" s="6" t="n"/>
       <c r="I216" s="6" t="n"/>
       <c r="J216" s="6" t="n"/>
+      <c r="K216" s="6" t="n"/>
+      <c r="L216" s="6" t="n"/>
+      <c r="M216" s="6" t="n"/>
+      <c r="N216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="n"/>
@@ -3238,6 +4133,10 @@
       <c r="H217" s="6" t="n"/>
       <c r="I217" s="6" t="n"/>
       <c r="J217" s="6" t="n"/>
+      <c r="K217" s="6" t="n"/>
+      <c r="L217" s="6" t="n"/>
+      <c r="M217" s="6" t="n"/>
+      <c r="N217" s="6" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="n"/>
@@ -3250,6 +4149,10 @@
       <c r="H218" s="6" t="n"/>
       <c r="I218" s="6" t="n"/>
       <c r="J218" s="6" t="n"/>
+      <c r="K218" s="6" t="n"/>
+      <c r="L218" s="6" t="n"/>
+      <c r="M218" s="6" t="n"/>
+      <c r="N218" s="6" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="n"/>
@@ -3262,6 +4165,10 @@
       <c r="H219" s="6" t="n"/>
       <c r="I219" s="6" t="n"/>
       <c r="J219" s="6" t="n"/>
+      <c r="K219" s="6" t="n"/>
+      <c r="L219" s="6" t="n"/>
+      <c r="M219" s="6" t="n"/>
+      <c r="N219" s="6" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="n"/>
@@ -3274,6 +4181,10 @@
       <c r="H220" s="6" t="n"/>
       <c r="I220" s="6" t="n"/>
       <c r="J220" s="6" t="n"/>
+      <c r="K220" s="6" t="n"/>
+      <c r="L220" s="6" t="n"/>
+      <c r="M220" s="6" t="n"/>
+      <c r="N220" s="6" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="n"/>
@@ -3286,6 +4197,10 @@
       <c r="H221" s="6" t="n"/>
       <c r="I221" s="6" t="n"/>
       <c r="J221" s="6" t="n"/>
+      <c r="K221" s="6" t="n"/>
+      <c r="L221" s="6" t="n"/>
+      <c r="M221" s="6" t="n"/>
+      <c r="N221" s="6" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="n"/>
@@ -3298,6 +4213,10 @@
       <c r="H222" s="6" t="n"/>
       <c r="I222" s="6" t="n"/>
       <c r="J222" s="6" t="n"/>
+      <c r="K222" s="6" t="n"/>
+      <c r="L222" s="6" t="n"/>
+      <c r="M222" s="6" t="n"/>
+      <c r="N222" s="6" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="n"/>
@@ -3310,6 +4229,10 @@
       <c r="H223" s="6" t="n"/>
       <c r="I223" s="6" t="n"/>
       <c r="J223" s="6" t="n"/>
+      <c r="K223" s="6" t="n"/>
+      <c r="L223" s="6" t="n"/>
+      <c r="M223" s="6" t="n"/>
+      <c r="N223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="n"/>
@@ -3322,6 +4245,10 @@
       <c r="H224" s="6" t="n"/>
       <c r="I224" s="6" t="n"/>
       <c r="J224" s="6" t="n"/>
+      <c r="K224" s="6" t="n"/>
+      <c r="L224" s="6" t="n"/>
+      <c r="M224" s="6" t="n"/>
+      <c r="N224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="n"/>
@@ -3334,6 +4261,10 @@
       <c r="H225" s="6" t="n"/>
       <c r="I225" s="6" t="n"/>
       <c r="J225" s="6" t="n"/>
+      <c r="K225" s="6" t="n"/>
+      <c r="L225" s="6" t="n"/>
+      <c r="M225" s="6" t="n"/>
+      <c r="N225" s="6" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="n"/>
@@ -3346,6 +4277,10 @@
       <c r="H226" s="6" t="n"/>
       <c r="I226" s="6" t="n"/>
       <c r="J226" s="6" t="n"/>
+      <c r="K226" s="6" t="n"/>
+      <c r="L226" s="6" t="n"/>
+      <c r="M226" s="6" t="n"/>
+      <c r="N226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="n"/>
@@ -3358,6 +4293,10 @@
       <c r="H227" s="6" t="n"/>
       <c r="I227" s="6" t="n"/>
       <c r="J227" s="6" t="n"/>
+      <c r="K227" s="6" t="n"/>
+      <c r="L227" s="6" t="n"/>
+      <c r="M227" s="6" t="n"/>
+      <c r="N227" s="6" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="n"/>
@@ -3370,6 +4309,10 @@
       <c r="H228" s="6" t="n"/>
       <c r="I228" s="6" t="n"/>
       <c r="J228" s="6" t="n"/>
+      <c r="K228" s="6" t="n"/>
+      <c r="L228" s="6" t="n"/>
+      <c r="M228" s="6" t="n"/>
+      <c r="N228" s="6" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="n"/>
@@ -3382,6 +4325,10 @@
       <c r="H229" s="6" t="n"/>
       <c r="I229" s="6" t="n"/>
       <c r="J229" s="6" t="n"/>
+      <c r="K229" s="6" t="n"/>
+      <c r="L229" s="6" t="n"/>
+      <c r="M229" s="6" t="n"/>
+      <c r="N229" s="6" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="n"/>
@@ -3394,6 +4341,10 @@
       <c r="H230" s="6" t="n"/>
       <c r="I230" s="6" t="n"/>
       <c r="J230" s="6" t="n"/>
+      <c r="K230" s="6" t="n"/>
+      <c r="L230" s="6" t="n"/>
+      <c r="M230" s="6" t="n"/>
+      <c r="N230" s="6" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="n"/>
@@ -3406,6 +4357,10 @@
       <c r="H231" s="6" t="n"/>
       <c r="I231" s="6" t="n"/>
       <c r="J231" s="6" t="n"/>
+      <c r="K231" s="6" t="n"/>
+      <c r="L231" s="6" t="n"/>
+      <c r="M231" s="6" t="n"/>
+      <c r="N231" s="6" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="n"/>
@@ -3418,6 +4373,10 @@
       <c r="H232" s="6" t="n"/>
       <c r="I232" s="6" t="n"/>
       <c r="J232" s="6" t="n"/>
+      <c r="K232" s="6" t="n"/>
+      <c r="L232" s="6" t="n"/>
+      <c r="M232" s="6" t="n"/>
+      <c r="N232" s="6" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="n"/>
@@ -3430,6 +4389,10 @@
       <c r="H233" s="6" t="n"/>
       <c r="I233" s="6" t="n"/>
       <c r="J233" s="6" t="n"/>
+      <c r="K233" s="6" t="n"/>
+      <c r="L233" s="6" t="n"/>
+      <c r="M233" s="6" t="n"/>
+      <c r="N233" s="6" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="n"/>
@@ -3442,6 +4405,10 @@
       <c r="H234" s="6" t="n"/>
       <c r="I234" s="6" t="n"/>
       <c r="J234" s="6" t="n"/>
+      <c r="K234" s="6" t="n"/>
+      <c r="L234" s="6" t="n"/>
+      <c r="M234" s="6" t="n"/>
+      <c r="N234" s="6" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="n"/>
@@ -3454,6 +4421,10 @@
       <c r="H235" s="6" t="n"/>
       <c r="I235" s="6" t="n"/>
       <c r="J235" s="6" t="n"/>
+      <c r="K235" s="6" t="n"/>
+      <c r="L235" s="6" t="n"/>
+      <c r="M235" s="6" t="n"/>
+      <c r="N235" s="6" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="n"/>
@@ -3466,6 +4437,10 @@
       <c r="H236" s="6" t="n"/>
       <c r="I236" s="6" t="n"/>
       <c r="J236" s="6" t="n"/>
+      <c r="K236" s="6" t="n"/>
+      <c r="L236" s="6" t="n"/>
+      <c r="M236" s="6" t="n"/>
+      <c r="N236" s="6" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="n"/>
@@ -3478,6 +4453,10 @@
       <c r="H237" s="6" t="n"/>
       <c r="I237" s="6" t="n"/>
       <c r="J237" s="6" t="n"/>
+      <c r="K237" s="6" t="n"/>
+      <c r="L237" s="6" t="n"/>
+      <c r="M237" s="6" t="n"/>
+      <c r="N237" s="6" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="n"/>
@@ -3490,6 +4469,10 @@
       <c r="H238" s="6" t="n"/>
       <c r="I238" s="6" t="n"/>
       <c r="J238" s="6" t="n"/>
+      <c r="K238" s="6" t="n"/>
+      <c r="L238" s="6" t="n"/>
+      <c r="M238" s="6" t="n"/>
+      <c r="N238" s="6" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="n"/>
@@ -3502,6 +4485,10 @@
       <c r="H239" s="6" t="n"/>
       <c r="I239" s="6" t="n"/>
       <c r="J239" s="6" t="n"/>
+      <c r="K239" s="6" t="n"/>
+      <c r="L239" s="6" t="n"/>
+      <c r="M239" s="6" t="n"/>
+      <c r="N239" s="6" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="n"/>
@@ -3514,6 +4501,10 @@
       <c r="H240" s="6" t="n"/>
       <c r="I240" s="6" t="n"/>
       <c r="J240" s="6" t="n"/>
+      <c r="K240" s="6" t="n"/>
+      <c r="L240" s="6" t="n"/>
+      <c r="M240" s="6" t="n"/>
+      <c r="N240" s="6" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="n"/>
@@ -3526,6 +4517,10 @@
       <c r="H241" s="6" t="n"/>
       <c r="I241" s="6" t="n"/>
       <c r="J241" s="6" t="n"/>
+      <c r="K241" s="6" t="n"/>
+      <c r="L241" s="6" t="n"/>
+      <c r="M241" s="6" t="n"/>
+      <c r="N241" s="6" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="n"/>
@@ -3538,6 +4533,10 @@
       <c r="H242" s="6" t="n"/>
       <c r="I242" s="6" t="n"/>
       <c r="J242" s="6" t="n"/>
+      <c r="K242" s="6" t="n"/>
+      <c r="L242" s="6" t="n"/>
+      <c r="M242" s="6" t="n"/>
+      <c r="N242" s="6" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="n"/>
@@ -3550,6 +4549,10 @@
       <c r="H243" s="6" t="n"/>
       <c r="I243" s="6" t="n"/>
       <c r="J243" s="6" t="n"/>
+      <c r="K243" s="6" t="n"/>
+      <c r="L243" s="6" t="n"/>
+      <c r="M243" s="6" t="n"/>
+      <c r="N243" s="6" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="n"/>
@@ -3562,6 +4565,10 @@
       <c r="H244" s="6" t="n"/>
       <c r="I244" s="6" t="n"/>
       <c r="J244" s="6" t="n"/>
+      <c r="K244" s="6" t="n"/>
+      <c r="L244" s="6" t="n"/>
+      <c r="M244" s="6" t="n"/>
+      <c r="N244" s="6" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="n"/>
@@ -3574,6 +4581,10 @@
       <c r="H245" s="6" t="n"/>
       <c r="I245" s="6" t="n"/>
       <c r="J245" s="6" t="n"/>
+      <c r="K245" s="6" t="n"/>
+      <c r="L245" s="6" t="n"/>
+      <c r="M245" s="6" t="n"/>
+      <c r="N245" s="6" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n"/>
@@ -3586,6 +4597,10 @@
       <c r="H246" s="6" t="n"/>
       <c r="I246" s="6" t="n"/>
       <c r="J246" s="6" t="n"/>
+      <c r="K246" s="6" t="n"/>
+      <c r="L246" s="6" t="n"/>
+      <c r="M246" s="6" t="n"/>
+      <c r="N246" s="6" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="n"/>
@@ -3598,6 +4613,10 @@
       <c r="H247" s="6" t="n"/>
       <c r="I247" s="6" t="n"/>
       <c r="J247" s="6" t="n"/>
+      <c r="K247" s="6" t="n"/>
+      <c r="L247" s="6" t="n"/>
+      <c r="M247" s="6" t="n"/>
+      <c r="N247" s="6" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="n"/>
@@ -3610,6 +4629,10 @@
       <c r="H248" s="6" t="n"/>
       <c r="I248" s="6" t="n"/>
       <c r="J248" s="6" t="n"/>
+      <c r="K248" s="6" t="n"/>
+      <c r="L248" s="6" t="n"/>
+      <c r="M248" s="6" t="n"/>
+      <c r="N248" s="6" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="n"/>
@@ -3622,6 +4645,10 @@
       <c r="H249" s="6" t="n"/>
       <c r="I249" s="6" t="n"/>
       <c r="J249" s="6" t="n"/>
+      <c r="K249" s="6" t="n"/>
+      <c r="L249" s="6" t="n"/>
+      <c r="M249" s="6" t="n"/>
+      <c r="N249" s="6" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="n"/>
@@ -3634,6 +4661,10 @@
       <c r="H250" s="6" t="n"/>
       <c r="I250" s="6" t="n"/>
       <c r="J250" s="6" t="n"/>
+      <c r="K250" s="6" t="n"/>
+      <c r="L250" s="6" t="n"/>
+      <c r="M250" s="6" t="n"/>
+      <c r="N250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="n"/>
@@ -3646,6 +4677,10 @@
       <c r="H251" s="6" t="n"/>
       <c r="I251" s="6" t="n"/>
       <c r="J251" s="6" t="n"/>
+      <c r="K251" s="6" t="n"/>
+      <c r="L251" s="6" t="n"/>
+      <c r="M251" s="6" t="n"/>
+      <c r="N251" s="6" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="n"/>
@@ -3658,6 +4693,10 @@
       <c r="H252" s="6" t="n"/>
       <c r="I252" s="6" t="n"/>
       <c r="J252" s="6" t="n"/>
+      <c r="K252" s="6" t="n"/>
+      <c r="L252" s="6" t="n"/>
+      <c r="M252" s="6" t="n"/>
+      <c r="N252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="n"/>
@@ -3670,6 +4709,10 @@
       <c r="H253" s="6" t="n"/>
       <c r="I253" s="6" t="n"/>
       <c r="J253" s="6" t="n"/>
+      <c r="K253" s="6" t="n"/>
+      <c r="L253" s="6" t="n"/>
+      <c r="M253" s="6" t="n"/>
+      <c r="N253" s="6" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="n"/>
@@ -3682,6 +4725,10 @@
       <c r="H254" s="6" t="n"/>
       <c r="I254" s="6" t="n"/>
       <c r="J254" s="6" t="n"/>
+      <c r="K254" s="6" t="n"/>
+      <c r="L254" s="6" t="n"/>
+      <c r="M254" s="6" t="n"/>
+      <c r="N254" s="6" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="n"/>
@@ -3694,6 +4741,10 @@
       <c r="H255" s="6" t="n"/>
       <c r="I255" s="6" t="n"/>
       <c r="J255" s="6" t="n"/>
+      <c r="K255" s="6" t="n"/>
+      <c r="L255" s="6" t="n"/>
+      <c r="M255" s="6" t="n"/>
+      <c r="N255" s="6" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="n"/>
@@ -3706,6 +4757,10 @@
       <c r="H256" s="6" t="n"/>
       <c r="I256" s="6" t="n"/>
       <c r="J256" s="6" t="n"/>
+      <c r="K256" s="6" t="n"/>
+      <c r="L256" s="6" t="n"/>
+      <c r="M256" s="6" t="n"/>
+      <c r="N256" s="6" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="n"/>
@@ -3718,6 +4773,10 @@
       <c r="H257" s="6" t="n"/>
       <c r="I257" s="6" t="n"/>
       <c r="J257" s="6" t="n"/>
+      <c r="K257" s="6" t="n"/>
+      <c r="L257" s="6" t="n"/>
+      <c r="M257" s="6" t="n"/>
+      <c r="N257" s="6" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="n"/>
@@ -3730,6 +4789,10 @@
       <c r="H258" s="6" t="n"/>
       <c r="I258" s="6" t="n"/>
       <c r="J258" s="6" t="n"/>
+      <c r="K258" s="6" t="n"/>
+      <c r="L258" s="6" t="n"/>
+      <c r="M258" s="6" t="n"/>
+      <c r="N258" s="6" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="n"/>
@@ -3742,6 +4805,10 @@
       <c r="H259" s="6" t="n"/>
       <c r="I259" s="6" t="n"/>
       <c r="J259" s="6" t="n"/>
+      <c r="K259" s="6" t="n"/>
+      <c r="L259" s="6" t="n"/>
+      <c r="M259" s="6" t="n"/>
+      <c r="N259" s="6" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="n"/>
@@ -3754,6 +4821,10 @@
       <c r="H260" s="6" t="n"/>
       <c r="I260" s="6" t="n"/>
       <c r="J260" s="6" t="n"/>
+      <c r="K260" s="6" t="n"/>
+      <c r="L260" s="6" t="n"/>
+      <c r="M260" s="6" t="n"/>
+      <c r="N260" s="6" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="n"/>
@@ -3766,6 +4837,10 @@
       <c r="H261" s="6" t="n"/>
       <c r="I261" s="6" t="n"/>
       <c r="J261" s="6" t="n"/>
+      <c r="K261" s="6" t="n"/>
+      <c r="L261" s="6" t="n"/>
+      <c r="M261" s="6" t="n"/>
+      <c r="N261" s="6" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="n"/>
@@ -3778,6 +4853,10 @@
       <c r="H262" s="6" t="n"/>
       <c r="I262" s="6" t="n"/>
       <c r="J262" s="6" t="n"/>
+      <c r="K262" s="6" t="n"/>
+      <c r="L262" s="6" t="n"/>
+      <c r="M262" s="6" t="n"/>
+      <c r="N262" s="6" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="n"/>
@@ -3790,6 +4869,10 @@
       <c r="H263" s="6" t="n"/>
       <c r="I263" s="6" t="n"/>
       <c r="J263" s="6" t="n"/>
+      <c r="K263" s="6" t="n"/>
+      <c r="L263" s="6" t="n"/>
+      <c r="M263" s="6" t="n"/>
+      <c r="N263" s="6" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="6" t="n"/>
@@ -3802,6 +4885,10 @@
       <c r="H264" s="6" t="n"/>
       <c r="I264" s="6" t="n"/>
       <c r="J264" s="6" t="n"/>
+      <c r="K264" s="6" t="n"/>
+      <c r="L264" s="6" t="n"/>
+      <c r="M264" s="6" t="n"/>
+      <c r="N264" s="6" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="n"/>
@@ -3814,6 +4901,10 @@
       <c r="H265" s="6" t="n"/>
       <c r="I265" s="6" t="n"/>
       <c r="J265" s="6" t="n"/>
+      <c r="K265" s="6" t="n"/>
+      <c r="L265" s="6" t="n"/>
+      <c r="M265" s="6" t="n"/>
+      <c r="N265" s="6" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="n"/>
@@ -3826,6 +4917,10 @@
       <c r="H266" s="6" t="n"/>
       <c r="I266" s="6" t="n"/>
       <c r="J266" s="6" t="n"/>
+      <c r="K266" s="6" t="n"/>
+      <c r="L266" s="6" t="n"/>
+      <c r="M266" s="6" t="n"/>
+      <c r="N266" s="6" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="n"/>
@@ -3838,6 +4933,10 @@
       <c r="H267" s="6" t="n"/>
       <c r="I267" s="6" t="n"/>
       <c r="J267" s="6" t="n"/>
+      <c r="K267" s="6" t="n"/>
+      <c r="L267" s="6" t="n"/>
+      <c r="M267" s="6" t="n"/>
+      <c r="N267" s="6" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="n"/>
@@ -3850,6 +4949,10 @@
       <c r="H268" s="6" t="n"/>
       <c r="I268" s="6" t="n"/>
       <c r="J268" s="6" t="n"/>
+      <c r="K268" s="6" t="n"/>
+      <c r="L268" s="6" t="n"/>
+      <c r="M268" s="6" t="n"/>
+      <c r="N268" s="6" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="n"/>
@@ -3862,6 +4965,10 @@
       <c r="H269" s="6" t="n"/>
       <c r="I269" s="6" t="n"/>
       <c r="J269" s="6" t="n"/>
+      <c r="K269" s="6" t="n"/>
+      <c r="L269" s="6" t="n"/>
+      <c r="M269" s="6" t="n"/>
+      <c r="N269" s="6" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="n"/>
@@ -3874,6 +4981,10 @@
       <c r="H270" s="6" t="n"/>
       <c r="I270" s="6" t="n"/>
       <c r="J270" s="6" t="n"/>
+      <c r="K270" s="6" t="n"/>
+      <c r="L270" s="6" t="n"/>
+      <c r="M270" s="6" t="n"/>
+      <c r="N270" s="6" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="n"/>
@@ -3886,6 +4997,10 @@
       <c r="H271" s="6" t="n"/>
       <c r="I271" s="6" t="n"/>
       <c r="J271" s="6" t="n"/>
+      <c r="K271" s="6" t="n"/>
+      <c r="L271" s="6" t="n"/>
+      <c r="M271" s="6" t="n"/>
+      <c r="N271" s="6" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="n"/>
@@ -3898,6 +5013,10 @@
       <c r="H272" s="6" t="n"/>
       <c r="I272" s="6" t="n"/>
       <c r="J272" s="6" t="n"/>
+      <c r="K272" s="6" t="n"/>
+      <c r="L272" s="6" t="n"/>
+      <c r="M272" s="6" t="n"/>
+      <c r="N272" s="6" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="n"/>
@@ -3910,6 +5029,10 @@
       <c r="H273" s="6" t="n"/>
       <c r="I273" s="6" t="n"/>
       <c r="J273" s="6" t="n"/>
+      <c r="K273" s="6" t="n"/>
+      <c r="L273" s="6" t="n"/>
+      <c r="M273" s="6" t="n"/>
+      <c r="N273" s="6" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="n"/>
@@ -3922,6 +5045,10 @@
       <c r="H274" s="6" t="n"/>
       <c r="I274" s="6" t="n"/>
       <c r="J274" s="6" t="n"/>
+      <c r="K274" s="6" t="n"/>
+      <c r="L274" s="6" t="n"/>
+      <c r="M274" s="6" t="n"/>
+      <c r="N274" s="6" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="n"/>
@@ -3934,6 +5061,10 @@
       <c r="H275" s="6" t="n"/>
       <c r="I275" s="6" t="n"/>
       <c r="J275" s="6" t="n"/>
+      <c r="K275" s="6" t="n"/>
+      <c r="L275" s="6" t="n"/>
+      <c r="M275" s="6" t="n"/>
+      <c r="N275" s="6" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="n"/>
@@ -3946,6 +5077,10 @@
       <c r="H276" s="6" t="n"/>
       <c r="I276" s="6" t="n"/>
       <c r="J276" s="6" t="n"/>
+      <c r="K276" s="6" t="n"/>
+      <c r="L276" s="6" t="n"/>
+      <c r="M276" s="6" t="n"/>
+      <c r="N276" s="6" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="n"/>
@@ -3958,6 +5093,10 @@
       <c r="H277" s="6" t="n"/>
       <c r="I277" s="6" t="n"/>
       <c r="J277" s="6" t="n"/>
+      <c r="K277" s="6" t="n"/>
+      <c r="L277" s="6" t="n"/>
+      <c r="M277" s="6" t="n"/>
+      <c r="N277" s="6" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="n"/>
@@ -3970,6 +5109,10 @@
       <c r="H278" s="6" t="n"/>
       <c r="I278" s="6" t="n"/>
       <c r="J278" s="6" t="n"/>
+      <c r="K278" s="6" t="n"/>
+      <c r="L278" s="6" t="n"/>
+      <c r="M278" s="6" t="n"/>
+      <c r="N278" s="6" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="n"/>
@@ -3982,6 +5125,10 @@
       <c r="H279" s="6" t="n"/>
       <c r="I279" s="6" t="n"/>
       <c r="J279" s="6" t="n"/>
+      <c r="K279" s="6" t="n"/>
+      <c r="L279" s="6" t="n"/>
+      <c r="M279" s="6" t="n"/>
+      <c r="N279" s="6" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="n"/>
@@ -3994,6 +5141,10 @@
       <c r="H280" s="6" t="n"/>
       <c r="I280" s="6" t="n"/>
       <c r="J280" s="6" t="n"/>
+      <c r="K280" s="6" t="n"/>
+      <c r="L280" s="6" t="n"/>
+      <c r="M280" s="6" t="n"/>
+      <c r="N280" s="6" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="n"/>
@@ -4006,6 +5157,10 @@
       <c r="H281" s="6" t="n"/>
       <c r="I281" s="6" t="n"/>
       <c r="J281" s="6" t="n"/>
+      <c r="K281" s="6" t="n"/>
+      <c r="L281" s="6" t="n"/>
+      <c r="M281" s="6" t="n"/>
+      <c r="N281" s="6" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="n"/>
@@ -4018,6 +5173,10 @@
       <c r="H282" s="6" t="n"/>
       <c r="I282" s="6" t="n"/>
       <c r="J282" s="6" t="n"/>
+      <c r="K282" s="6" t="n"/>
+      <c r="L282" s="6" t="n"/>
+      <c r="M282" s="6" t="n"/>
+      <c r="N282" s="6" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="n"/>
@@ -4030,6 +5189,10 @@
       <c r="H283" s="6" t="n"/>
       <c r="I283" s="6" t="n"/>
       <c r="J283" s="6" t="n"/>
+      <c r="K283" s="6" t="n"/>
+      <c r="L283" s="6" t="n"/>
+      <c r="M283" s="6" t="n"/>
+      <c r="N283" s="6" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="n"/>
@@ -4042,6 +5205,10 @@
       <c r="H284" s="6" t="n"/>
       <c r="I284" s="6" t="n"/>
       <c r="J284" s="6" t="n"/>
+      <c r="K284" s="6" t="n"/>
+      <c r="L284" s="6" t="n"/>
+      <c r="M284" s="6" t="n"/>
+      <c r="N284" s="6" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="n"/>
@@ -4054,6 +5221,10 @@
       <c r="H285" s="6" t="n"/>
       <c r="I285" s="6" t="n"/>
       <c r="J285" s="6" t="n"/>
+      <c r="K285" s="6" t="n"/>
+      <c r="L285" s="6" t="n"/>
+      <c r="M285" s="6" t="n"/>
+      <c r="N285" s="6" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="n"/>
@@ -4066,6 +5237,10 @@
       <c r="H286" s="6" t="n"/>
       <c r="I286" s="6" t="n"/>
       <c r="J286" s="6" t="n"/>
+      <c r="K286" s="6" t="n"/>
+      <c r="L286" s="6" t="n"/>
+      <c r="M286" s="6" t="n"/>
+      <c r="N286" s="6" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="n"/>
@@ -4078,6 +5253,10 @@
       <c r="H287" s="6" t="n"/>
       <c r="I287" s="6" t="n"/>
       <c r="J287" s="6" t="n"/>
+      <c r="K287" s="6" t="n"/>
+      <c r="L287" s="6" t="n"/>
+      <c r="M287" s="6" t="n"/>
+      <c r="N287" s="6" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="n"/>
@@ -4090,6 +5269,10 @@
       <c r="H288" s="6" t="n"/>
       <c r="I288" s="6" t="n"/>
       <c r="J288" s="6" t="n"/>
+      <c r="K288" s="6" t="n"/>
+      <c r="L288" s="6" t="n"/>
+      <c r="M288" s="6" t="n"/>
+      <c r="N288" s="6" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="n"/>
@@ -4102,6 +5285,10 @@
       <c r="H289" s="6" t="n"/>
       <c r="I289" s="6" t="n"/>
       <c r="J289" s="6" t="n"/>
+      <c r="K289" s="6" t="n"/>
+      <c r="L289" s="6" t="n"/>
+      <c r="M289" s="6" t="n"/>
+      <c r="N289" s="6" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="6" t="n"/>
@@ -4114,6 +5301,10 @@
       <c r="H290" s="6" t="n"/>
       <c r="I290" s="6" t="n"/>
       <c r="J290" s="6" t="n"/>
+      <c r="K290" s="6" t="n"/>
+      <c r="L290" s="6" t="n"/>
+      <c r="M290" s="6" t="n"/>
+      <c r="N290" s="6" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="n"/>
@@ -4126,6 +5317,10 @@
       <c r="H291" s="6" t="n"/>
       <c r="I291" s="6" t="n"/>
       <c r="J291" s="6" t="n"/>
+      <c r="K291" s="6" t="n"/>
+      <c r="L291" s="6" t="n"/>
+      <c r="M291" s="6" t="n"/>
+      <c r="N291" s="6" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="6" t="n"/>
@@ -4138,6 +5333,10 @@
       <c r="H292" s="6" t="n"/>
       <c r="I292" s="6" t="n"/>
       <c r="J292" s="6" t="n"/>
+      <c r="K292" s="6" t="n"/>
+      <c r="L292" s="6" t="n"/>
+      <c r="M292" s="6" t="n"/>
+      <c r="N292" s="6" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="n"/>
@@ -4150,6 +5349,10 @@
       <c r="H293" s="6" t="n"/>
       <c r="I293" s="6" t="n"/>
       <c r="J293" s="6" t="n"/>
+      <c r="K293" s="6" t="n"/>
+      <c r="L293" s="6" t="n"/>
+      <c r="M293" s="6" t="n"/>
+      <c r="N293" s="6" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="n"/>
@@ -4162,6 +5365,10 @@
       <c r="H294" s="6" t="n"/>
       <c r="I294" s="6" t="n"/>
       <c r="J294" s="6" t="n"/>
+      <c r="K294" s="6" t="n"/>
+      <c r="L294" s="6" t="n"/>
+      <c r="M294" s="6" t="n"/>
+      <c r="N294" s="6" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="n"/>
@@ -4174,6 +5381,10 @@
       <c r="H295" s="6" t="n"/>
       <c r="I295" s="6" t="n"/>
       <c r="J295" s="6" t="n"/>
+      <c r="K295" s="6" t="n"/>
+      <c r="L295" s="6" t="n"/>
+      <c r="M295" s="6" t="n"/>
+      <c r="N295" s="6" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="6" t="n"/>
@@ -4186,6 +5397,10 @@
       <c r="H296" s="6" t="n"/>
       <c r="I296" s="6" t="n"/>
       <c r="J296" s="6" t="n"/>
+      <c r="K296" s="6" t="n"/>
+      <c r="L296" s="6" t="n"/>
+      <c r="M296" s="6" t="n"/>
+      <c r="N296" s="6" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="n"/>
@@ -4198,6 +5413,10 @@
       <c r="H297" s="6" t="n"/>
       <c r="I297" s="6" t="n"/>
       <c r="J297" s="6" t="n"/>
+      <c r="K297" s="6" t="n"/>
+      <c r="L297" s="6" t="n"/>
+      <c r="M297" s="6" t="n"/>
+      <c r="N297" s="6" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="6" t="n"/>
@@ -4210,6 +5429,10 @@
       <c r="H298" s="6" t="n"/>
       <c r="I298" s="6" t="n"/>
       <c r="J298" s="6" t="n"/>
+      <c r="K298" s="6" t="n"/>
+      <c r="L298" s="6" t="n"/>
+      <c r="M298" s="6" t="n"/>
+      <c r="N298" s="6" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="n"/>
@@ -4222,6 +5445,10 @@
       <c r="H299" s="6" t="n"/>
       <c r="I299" s="6" t="n"/>
       <c r="J299" s="6" t="n"/>
+      <c r="K299" s="6" t="n"/>
+      <c r="L299" s="6" t="n"/>
+      <c r="M299" s="6" t="n"/>
+      <c r="N299" s="6" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="6" t="n"/>
@@ -4234,6 +5461,10 @@
       <c r="H300" s="6" t="n"/>
       <c r="I300" s="6" t="n"/>
       <c r="J300" s="6" t="n"/>
+      <c r="K300" s="6" t="n"/>
+      <c r="L300" s="6" t="n"/>
+      <c r="M300" s="6" t="n"/>
+      <c r="N300" s="6" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="n"/>
@@ -4246,6 +5477,10 @@
       <c r="H301" s="6" t="n"/>
       <c r="I301" s="6" t="n"/>
       <c r="J301" s="6" t="n"/>
+      <c r="K301" s="6" t="n"/>
+      <c r="L301" s="6" t="n"/>
+      <c r="M301" s="6" t="n"/>
+      <c r="N301" s="6" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="6" t="n"/>
@@ -4258,6 +5493,10 @@
       <c r="H302" s="6" t="n"/>
       <c r="I302" s="6" t="n"/>
       <c r="J302" s="6" t="n"/>
+      <c r="K302" s="6" t="n"/>
+      <c r="L302" s="6" t="n"/>
+      <c r="M302" s="6" t="n"/>
+      <c r="N302" s="6" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="6" t="n"/>
@@ -4270,6 +5509,10 @@
       <c r="H303" s="6" t="n"/>
       <c r="I303" s="6" t="n"/>
       <c r="J303" s="6" t="n"/>
+      <c r="K303" s="6" t="n"/>
+      <c r="L303" s="6" t="n"/>
+      <c r="M303" s="6" t="n"/>
+      <c r="N303" s="6" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="6" t="n"/>
@@ -4282,6 +5525,10 @@
       <c r="H304" s="6" t="n"/>
       <c r="I304" s="6" t="n"/>
       <c r="J304" s="6" t="n"/>
+      <c r="K304" s="6" t="n"/>
+      <c r="L304" s="6" t="n"/>
+      <c r="M304" s="6" t="n"/>
+      <c r="N304" s="6" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="6" t="n"/>
@@ -4294,6 +5541,10 @@
       <c r="H305" s="6" t="n"/>
       <c r="I305" s="6" t="n"/>
       <c r="J305" s="6" t="n"/>
+      <c r="K305" s="6" t="n"/>
+      <c r="L305" s="6" t="n"/>
+      <c r="M305" s="6" t="n"/>
+      <c r="N305" s="6" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="6" t="n"/>
@@ -4306,6 +5557,10 @@
       <c r="H306" s="6" t="n"/>
       <c r="I306" s="6" t="n"/>
       <c r="J306" s="6" t="n"/>
+      <c r="K306" s="6" t="n"/>
+      <c r="L306" s="6" t="n"/>
+      <c r="M306" s="6" t="n"/>
+      <c r="N306" s="6" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="6" t="n"/>
@@ -4318,6 +5573,10 @@
       <c r="H307" s="6" t="n"/>
       <c r="I307" s="6" t="n"/>
       <c r="J307" s="6" t="n"/>
+      <c r="K307" s="6" t="n"/>
+      <c r="L307" s="6" t="n"/>
+      <c r="M307" s="6" t="n"/>
+      <c r="N307" s="6" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="6" t="n"/>
@@ -4330,6 +5589,10 @@
       <c r="H308" s="6" t="n"/>
       <c r="I308" s="6" t="n"/>
       <c r="J308" s="6" t="n"/>
+      <c r="K308" s="6" t="n"/>
+      <c r="L308" s="6" t="n"/>
+      <c r="M308" s="6" t="n"/>
+      <c r="N308" s="6" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="6" t="n"/>
@@ -4342,6 +5605,10 @@
       <c r="H309" s="6" t="n"/>
       <c r="I309" s="6" t="n"/>
       <c r="J309" s="6" t="n"/>
+      <c r="K309" s="6" t="n"/>
+      <c r="L309" s="6" t="n"/>
+      <c r="M309" s="6" t="n"/>
+      <c r="N309" s="6" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="6" t="n"/>
@@ -4354,6 +5621,10 @@
       <c r="H310" s="6" t="n"/>
       <c r="I310" s="6" t="n"/>
       <c r="J310" s="6" t="n"/>
+      <c r="K310" s="6" t="n"/>
+      <c r="L310" s="6" t="n"/>
+      <c r="M310" s="6" t="n"/>
+      <c r="N310" s="6" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="6" t="n"/>
@@ -4366,6 +5637,10 @@
       <c r="H311" s="6" t="n"/>
       <c r="I311" s="6" t="n"/>
       <c r="J311" s="6" t="n"/>
+      <c r="K311" s="6" t="n"/>
+      <c r="L311" s="6" t="n"/>
+      <c r="M311" s="6" t="n"/>
+      <c r="N311" s="6" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="6" t="n"/>
@@ -4378,6 +5653,10 @@
       <c r="H312" s="6" t="n"/>
       <c r="I312" s="6" t="n"/>
       <c r="J312" s="6" t="n"/>
+      <c r="K312" s="6" t="n"/>
+      <c r="L312" s="6" t="n"/>
+      <c r="M312" s="6" t="n"/>
+      <c r="N312" s="6" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="6" t="n"/>
@@ -4390,6 +5669,10 @@
       <c r="H313" s="6" t="n"/>
       <c r="I313" s="6" t="n"/>
       <c r="J313" s="6" t="n"/>
+      <c r="K313" s="6" t="n"/>
+      <c r="L313" s="6" t="n"/>
+      <c r="M313" s="6" t="n"/>
+      <c r="N313" s="6" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="6" t="n"/>
@@ -4402,6 +5685,10 @@
       <c r="H314" s="6" t="n"/>
       <c r="I314" s="6" t="n"/>
       <c r="J314" s="6" t="n"/>
+      <c r="K314" s="6" t="n"/>
+      <c r="L314" s="6" t="n"/>
+      <c r="M314" s="6" t="n"/>
+      <c r="N314" s="6" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="6" t="n"/>
@@ -4414,6 +5701,10 @@
       <c r="H315" s="6" t="n"/>
       <c r="I315" s="6" t="n"/>
       <c r="J315" s="6" t="n"/>
+      <c r="K315" s="6" t="n"/>
+      <c r="L315" s="6" t="n"/>
+      <c r="M315" s="6" t="n"/>
+      <c r="N315" s="6" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="6" t="n"/>
@@ -4426,6 +5717,10 @@
       <c r="H316" s="6" t="n"/>
       <c r="I316" s="6" t="n"/>
       <c r="J316" s="6" t="n"/>
+      <c r="K316" s="6" t="n"/>
+      <c r="L316" s="6" t="n"/>
+      <c r="M316" s="6" t="n"/>
+      <c r="N316" s="6" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="6" t="n"/>
@@ -4438,6 +5733,10 @@
       <c r="H317" s="6" t="n"/>
       <c r="I317" s="6" t="n"/>
       <c r="J317" s="6" t="n"/>
+      <c r="K317" s="6" t="n"/>
+      <c r="L317" s="6" t="n"/>
+      <c r="M317" s="6" t="n"/>
+      <c r="N317" s="6" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="6" t="n"/>
@@ -4450,6 +5749,10 @@
       <c r="H318" s="6" t="n"/>
       <c r="I318" s="6" t="n"/>
       <c r="J318" s="6" t="n"/>
+      <c r="K318" s="6" t="n"/>
+      <c r="L318" s="6" t="n"/>
+      <c r="M318" s="6" t="n"/>
+      <c r="N318" s="6" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="6" t="n"/>
@@ -4462,6 +5765,10 @@
       <c r="H319" s="6" t="n"/>
       <c r="I319" s="6" t="n"/>
       <c r="J319" s="6" t="n"/>
+      <c r="K319" s="6" t="n"/>
+      <c r="L319" s="6" t="n"/>
+      <c r="M319" s="6" t="n"/>
+      <c r="N319" s="6" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="6" t="n"/>
@@ -4474,6 +5781,10 @@
       <c r="H320" s="6" t="n"/>
       <c r="I320" s="6" t="n"/>
       <c r="J320" s="6" t="n"/>
+      <c r="K320" s="6" t="n"/>
+      <c r="L320" s="6" t="n"/>
+      <c r="M320" s="6" t="n"/>
+      <c r="N320" s="6" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="6" t="n"/>
@@ -4486,6 +5797,10 @@
       <c r="H321" s="6" t="n"/>
       <c r="I321" s="6" t="n"/>
       <c r="J321" s="6" t="n"/>
+      <c r="K321" s="6" t="n"/>
+      <c r="L321" s="6" t="n"/>
+      <c r="M321" s="6" t="n"/>
+      <c r="N321" s="6" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="6" t="n"/>
@@ -4498,6 +5813,10 @@
       <c r="H322" s="6" t="n"/>
       <c r="I322" s="6" t="n"/>
       <c r="J322" s="6" t="n"/>
+      <c r="K322" s="6" t="n"/>
+      <c r="L322" s="6" t="n"/>
+      <c r="M322" s="6" t="n"/>
+      <c r="N322" s="6" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="6" t="n"/>
@@ -4510,6 +5829,10 @@
       <c r="H323" s="6" t="n"/>
       <c r="I323" s="6" t="n"/>
       <c r="J323" s="6" t="n"/>
+      <c r="K323" s="6" t="n"/>
+      <c r="L323" s="6" t="n"/>
+      <c r="M323" s="6" t="n"/>
+      <c r="N323" s="6" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="6" t="n"/>
@@ -4522,6 +5845,10 @@
       <c r="H324" s="6" t="n"/>
       <c r="I324" s="6" t="n"/>
       <c r="J324" s="6" t="n"/>
+      <c r="K324" s="6" t="n"/>
+      <c r="L324" s="6" t="n"/>
+      <c r="M324" s="6" t="n"/>
+      <c r="N324" s="6" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="6" t="n"/>
@@ -4534,6 +5861,10 @@
       <c r="H325" s="6" t="n"/>
       <c r="I325" s="6" t="n"/>
       <c r="J325" s="6" t="n"/>
+      <c r="K325" s="6" t="n"/>
+      <c r="L325" s="6" t="n"/>
+      <c r="M325" s="6" t="n"/>
+      <c r="N325" s="6" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="6" t="n"/>
@@ -4546,6 +5877,10 @@
       <c r="H326" s="6" t="n"/>
       <c r="I326" s="6" t="n"/>
       <c r="J326" s="6" t="n"/>
+      <c r="K326" s="6" t="n"/>
+      <c r="L326" s="6" t="n"/>
+      <c r="M326" s="6" t="n"/>
+      <c r="N326" s="6" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="6" t="n"/>
@@ -4558,6 +5893,10 @@
       <c r="H327" s="6" t="n"/>
       <c r="I327" s="6" t="n"/>
       <c r="J327" s="6" t="n"/>
+      <c r="K327" s="6" t="n"/>
+      <c r="L327" s="6" t="n"/>
+      <c r="M327" s="6" t="n"/>
+      <c r="N327" s="6" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="6" t="n"/>
@@ -4570,6 +5909,10 @@
       <c r="H328" s="6" t="n"/>
       <c r="I328" s="6" t="n"/>
       <c r="J328" s="6" t="n"/>
+      <c r="K328" s="6" t="n"/>
+      <c r="L328" s="6" t="n"/>
+      <c r="M328" s="6" t="n"/>
+      <c r="N328" s="6" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="6" t="n"/>
@@ -4582,6 +5925,10 @@
       <c r="H329" s="6" t="n"/>
       <c r="I329" s="6" t="n"/>
       <c r="J329" s="6" t="n"/>
+      <c r="K329" s="6" t="n"/>
+      <c r="L329" s="6" t="n"/>
+      <c r="M329" s="6" t="n"/>
+      <c r="N329" s="6" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="6" t="n"/>
@@ -4594,6 +5941,10 @@
       <c r="H330" s="6" t="n"/>
       <c r="I330" s="6" t="n"/>
       <c r="J330" s="6" t="n"/>
+      <c r="K330" s="6" t="n"/>
+      <c r="L330" s="6" t="n"/>
+      <c r="M330" s="6" t="n"/>
+      <c r="N330" s="6" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="6" t="n"/>
@@ -4606,6 +5957,10 @@
       <c r="H331" s="6" t="n"/>
       <c r="I331" s="6" t="n"/>
       <c r="J331" s="6" t="n"/>
+      <c r="K331" s="6" t="n"/>
+      <c r="L331" s="6" t="n"/>
+      <c r="M331" s="6" t="n"/>
+      <c r="N331" s="6" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="6" t="n"/>
@@ -4618,6 +5973,10 @@
       <c r="H332" s="6" t="n"/>
       <c r="I332" s="6" t="n"/>
       <c r="J332" s="6" t="n"/>
+      <c r="K332" s="6" t="n"/>
+      <c r="L332" s="6" t="n"/>
+      <c r="M332" s="6" t="n"/>
+      <c r="N332" s="6" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="6" t="n"/>
@@ -4630,6 +5989,10 @@
       <c r="H333" s="6" t="n"/>
       <c r="I333" s="6" t="n"/>
       <c r="J333" s="6" t="n"/>
+      <c r="K333" s="6" t="n"/>
+      <c r="L333" s="6" t="n"/>
+      <c r="M333" s="6" t="n"/>
+      <c r="N333" s="6" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="6" t="n"/>
@@ -4642,6 +6005,10 @@
       <c r="H334" s="6" t="n"/>
       <c r="I334" s="6" t="n"/>
       <c r="J334" s="6" t="n"/>
+      <c r="K334" s="6" t="n"/>
+      <c r="L334" s="6" t="n"/>
+      <c r="M334" s="6" t="n"/>
+      <c r="N334" s="6" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="6" t="n"/>
@@ -4654,6 +6021,10 @@
       <c r="H335" s="6" t="n"/>
       <c r="I335" s="6" t="n"/>
       <c r="J335" s="6" t="n"/>
+      <c r="K335" s="6" t="n"/>
+      <c r="L335" s="6" t="n"/>
+      <c r="M335" s="6" t="n"/>
+      <c r="N335" s="6" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="6" t="n"/>
@@ -4666,6 +6037,10 @@
       <c r="H336" s="6" t="n"/>
       <c r="I336" s="6" t="n"/>
       <c r="J336" s="6" t="n"/>
+      <c r="K336" s="6" t="n"/>
+      <c r="L336" s="6" t="n"/>
+      <c r="M336" s="6" t="n"/>
+      <c r="N336" s="6" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="6" t="n"/>
@@ -4678,6 +6053,10 @@
       <c r="H337" s="6" t="n"/>
       <c r="I337" s="6" t="n"/>
       <c r="J337" s="6" t="n"/>
+      <c r="K337" s="6" t="n"/>
+      <c r="L337" s="6" t="n"/>
+      <c r="M337" s="6" t="n"/>
+      <c r="N337" s="6" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="6" t="n"/>
@@ -4690,6 +6069,10 @@
       <c r="H338" s="6" t="n"/>
       <c r="I338" s="6" t="n"/>
       <c r="J338" s="6" t="n"/>
+      <c r="K338" s="6" t="n"/>
+      <c r="L338" s="6" t="n"/>
+      <c r="M338" s="6" t="n"/>
+      <c r="N338" s="6" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="6" t="n"/>
@@ -4702,6 +6085,10 @@
       <c r="H339" s="6" t="n"/>
       <c r="I339" s="6" t="n"/>
       <c r="J339" s="6" t="n"/>
+      <c r="K339" s="6" t="n"/>
+      <c r="L339" s="6" t="n"/>
+      <c r="M339" s="6" t="n"/>
+      <c r="N339" s="6" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="6" t="n"/>
@@ -4714,6 +6101,10 @@
       <c r="H340" s="6" t="n"/>
       <c r="I340" s="6" t="n"/>
       <c r="J340" s="6" t="n"/>
+      <c r="K340" s="6" t="n"/>
+      <c r="L340" s="6" t="n"/>
+      <c r="M340" s="6" t="n"/>
+      <c r="N340" s="6" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="6" t="n"/>
@@ -4726,6 +6117,10 @@
       <c r="H341" s="6" t="n"/>
       <c r="I341" s="6" t="n"/>
       <c r="J341" s="6" t="n"/>
+      <c r="K341" s="6" t="n"/>
+      <c r="L341" s="6" t="n"/>
+      <c r="M341" s="6" t="n"/>
+      <c r="N341" s="6" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="6" t="n"/>
@@ -4738,6 +6133,10 @@
       <c r="H342" s="6" t="n"/>
       <c r="I342" s="6" t="n"/>
       <c r="J342" s="6" t="n"/>
+      <c r="K342" s="6" t="n"/>
+      <c r="L342" s="6" t="n"/>
+      <c r="M342" s="6" t="n"/>
+      <c r="N342" s="6" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="n"/>
@@ -4750,6 +6149,10 @@
       <c r="H343" s="6" t="n"/>
       <c r="I343" s="6" t="n"/>
       <c r="J343" s="6" t="n"/>
+      <c r="K343" s="6" t="n"/>
+      <c r="L343" s="6" t="n"/>
+      <c r="M343" s="6" t="n"/>
+      <c r="N343" s="6" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="6" t="n"/>
@@ -4762,6 +6165,10 @@
       <c r="H344" s="6" t="n"/>
       <c r="I344" s="6" t="n"/>
       <c r="J344" s="6" t="n"/>
+      <c r="K344" s="6" t="n"/>
+      <c r="L344" s="6" t="n"/>
+      <c r="M344" s="6" t="n"/>
+      <c r="N344" s="6" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="6" t="n"/>
@@ -4774,6 +6181,10 @@
       <c r="H345" s="6" t="n"/>
       <c r="I345" s="6" t="n"/>
       <c r="J345" s="6" t="n"/>
+      <c r="K345" s="6" t="n"/>
+      <c r="L345" s="6" t="n"/>
+      <c r="M345" s="6" t="n"/>
+      <c r="N345" s="6" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="6" t="n"/>
@@ -4786,6 +6197,10 @@
       <c r="H346" s="6" t="n"/>
       <c r="I346" s="6" t="n"/>
       <c r="J346" s="6" t="n"/>
+      <c r="K346" s="6" t="n"/>
+      <c r="L346" s="6" t="n"/>
+      <c r="M346" s="6" t="n"/>
+      <c r="N346" s="6" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="6" t="n"/>
@@ -4798,6 +6213,10 @@
       <c r="H347" s="6" t="n"/>
       <c r="I347" s="6" t="n"/>
       <c r="J347" s="6" t="n"/>
+      <c r="K347" s="6" t="n"/>
+      <c r="L347" s="6" t="n"/>
+      <c r="M347" s="6" t="n"/>
+      <c r="N347" s="6" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="6" t="n"/>
@@ -4810,6 +6229,10 @@
       <c r="H348" s="6" t="n"/>
       <c r="I348" s="6" t="n"/>
       <c r="J348" s="6" t="n"/>
+      <c r="K348" s="6" t="n"/>
+      <c r="L348" s="6" t="n"/>
+      <c r="M348" s="6" t="n"/>
+      <c r="N348" s="6" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="6" t="n"/>
@@ -4822,6 +6245,10 @@
       <c r="H349" s="6" t="n"/>
       <c r="I349" s="6" t="n"/>
       <c r="J349" s="6" t="n"/>
+      <c r="K349" s="6" t="n"/>
+      <c r="L349" s="6" t="n"/>
+      <c r="M349" s="6" t="n"/>
+      <c r="N349" s="6" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="6" t="n"/>
@@ -4834,6 +6261,10 @@
       <c r="H350" s="6" t="n"/>
       <c r="I350" s="6" t="n"/>
       <c r="J350" s="6" t="n"/>
+      <c r="K350" s="6" t="n"/>
+      <c r="L350" s="6" t="n"/>
+      <c r="M350" s="6" t="n"/>
+      <c r="N350" s="6" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="6" t="n"/>
@@ -4846,6 +6277,10 @@
       <c r="H351" s="6" t="n"/>
       <c r="I351" s="6" t="n"/>
       <c r="J351" s="6" t="n"/>
+      <c r="K351" s="6" t="n"/>
+      <c r="L351" s="6" t="n"/>
+      <c r="M351" s="6" t="n"/>
+      <c r="N351" s="6" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="6" t="n"/>
@@ -4858,6 +6293,10 @@
       <c r="H352" s="6" t="n"/>
       <c r="I352" s="6" t="n"/>
       <c r="J352" s="6" t="n"/>
+      <c r="K352" s="6" t="n"/>
+      <c r="L352" s="6" t="n"/>
+      <c r="M352" s="6" t="n"/>
+      <c r="N352" s="6" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="6" t="n"/>
@@ -4870,6 +6309,10 @@
       <c r="H353" s="6" t="n"/>
       <c r="I353" s="6" t="n"/>
       <c r="J353" s="6" t="n"/>
+      <c r="K353" s="6" t="n"/>
+      <c r="L353" s="6" t="n"/>
+      <c r="M353" s="6" t="n"/>
+      <c r="N353" s="6" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="6" t="n"/>
@@ -4882,6 +6325,10 @@
       <c r="H354" s="6" t="n"/>
       <c r="I354" s="6" t="n"/>
       <c r="J354" s="6" t="n"/>
+      <c r="K354" s="6" t="n"/>
+      <c r="L354" s="6" t="n"/>
+      <c r="M354" s="6" t="n"/>
+      <c r="N354" s="6" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="6" t="n"/>
@@ -4894,6 +6341,10 @@
       <c r="H355" s="6" t="n"/>
       <c r="I355" s="6" t="n"/>
       <c r="J355" s="6" t="n"/>
+      <c r="K355" s="6" t="n"/>
+      <c r="L355" s="6" t="n"/>
+      <c r="M355" s="6" t="n"/>
+      <c r="N355" s="6" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="6" t="n"/>
@@ -4906,6 +6357,10 @@
       <c r="H356" s="6" t="n"/>
       <c r="I356" s="6" t="n"/>
       <c r="J356" s="6" t="n"/>
+      <c r="K356" s="6" t="n"/>
+      <c r="L356" s="6" t="n"/>
+      <c r="M356" s="6" t="n"/>
+      <c r="N356" s="6" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="6" t="n"/>
@@ -4918,6 +6373,10 @@
       <c r="H357" s="6" t="n"/>
       <c r="I357" s="6" t="n"/>
       <c r="J357" s="6" t="n"/>
+      <c r="K357" s="6" t="n"/>
+      <c r="L357" s="6" t="n"/>
+      <c r="M357" s="6" t="n"/>
+      <c r="N357" s="6" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="6" t="n"/>
@@ -4930,6 +6389,10 @@
       <c r="H358" s="6" t="n"/>
       <c r="I358" s="6" t="n"/>
       <c r="J358" s="6" t="n"/>
+      <c r="K358" s="6" t="n"/>
+      <c r="L358" s="6" t="n"/>
+      <c r="M358" s="6" t="n"/>
+      <c r="N358" s="6" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="6" t="n"/>
@@ -4942,6 +6405,10 @@
       <c r="H359" s="6" t="n"/>
       <c r="I359" s="6" t="n"/>
       <c r="J359" s="6" t="n"/>
+      <c r="K359" s="6" t="n"/>
+      <c r="L359" s="6" t="n"/>
+      <c r="M359" s="6" t="n"/>
+      <c r="N359" s="6" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="6" t="n"/>
@@ -4954,6 +6421,10 @@
       <c r="H360" s="6" t="n"/>
       <c r="I360" s="6" t="n"/>
       <c r="J360" s="6" t="n"/>
+      <c r="K360" s="6" t="n"/>
+      <c r="L360" s="6" t="n"/>
+      <c r="M360" s="6" t="n"/>
+      <c r="N360" s="6" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="6" t="n"/>
@@ -4966,6 +6437,10 @@
       <c r="H361" s="6" t="n"/>
       <c r="I361" s="6" t="n"/>
       <c r="J361" s="6" t="n"/>
+      <c r="K361" s="6" t="n"/>
+      <c r="L361" s="6" t="n"/>
+      <c r="M361" s="6" t="n"/>
+      <c r="N361" s="6" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="6" t="n"/>
@@ -4978,6 +6453,10 @@
       <c r="H362" s="6" t="n"/>
       <c r="I362" s="6" t="n"/>
       <c r="J362" s="6" t="n"/>
+      <c r="K362" s="6" t="n"/>
+      <c r="L362" s="6" t="n"/>
+      <c r="M362" s="6" t="n"/>
+      <c r="N362" s="6" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="6" t="n"/>
@@ -4990,6 +6469,10 @@
       <c r="H363" s="6" t="n"/>
       <c r="I363" s="6" t="n"/>
       <c r="J363" s="6" t="n"/>
+      <c r="K363" s="6" t="n"/>
+      <c r="L363" s="6" t="n"/>
+      <c r="M363" s="6" t="n"/>
+      <c r="N363" s="6" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="6" t="n"/>
@@ -5002,6 +6485,10 @@
       <c r="H364" s="6" t="n"/>
       <c r="I364" s="6" t="n"/>
       <c r="J364" s="6" t="n"/>
+      <c r="K364" s="6" t="n"/>
+      <c r="L364" s="6" t="n"/>
+      <c r="M364" s="6" t="n"/>
+      <c r="N364" s="6" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="6" t="n"/>
@@ -5014,6 +6501,10 @@
       <c r="H365" s="6" t="n"/>
       <c r="I365" s="6" t="n"/>
       <c r="J365" s="6" t="n"/>
+      <c r="K365" s="6" t="n"/>
+      <c r="L365" s="6" t="n"/>
+      <c r="M365" s="6" t="n"/>
+      <c r="N365" s="6" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="6" t="n"/>
@@ -5026,6 +6517,10 @@
       <c r="H366" s="6" t="n"/>
       <c r="I366" s="6" t="n"/>
       <c r="J366" s="6" t="n"/>
+      <c r="K366" s="6" t="n"/>
+      <c r="L366" s="6" t="n"/>
+      <c r="M366" s="6" t="n"/>
+      <c r="N366" s="6" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="6" t="n"/>
@@ -5038,6 +6533,10 @@
       <c r="H367" s="6" t="n"/>
       <c r="I367" s="6" t="n"/>
       <c r="J367" s="6" t="n"/>
+      <c r="K367" s="6" t="n"/>
+      <c r="L367" s="6" t="n"/>
+      <c r="M367" s="6" t="n"/>
+      <c r="N367" s="6" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="6" t="n"/>
@@ -5050,6 +6549,10 @@
       <c r="H368" s="6" t="n"/>
       <c r="I368" s="6" t="n"/>
       <c r="J368" s="6" t="n"/>
+      <c r="K368" s="6" t="n"/>
+      <c r="L368" s="6" t="n"/>
+      <c r="M368" s="6" t="n"/>
+      <c r="N368" s="6" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="6" t="n"/>
@@ -5062,6 +6565,10 @@
       <c r="H369" s="6" t="n"/>
       <c r="I369" s="6" t="n"/>
       <c r="J369" s="6" t="n"/>
+      <c r="K369" s="6" t="n"/>
+      <c r="L369" s="6" t="n"/>
+      <c r="M369" s="6" t="n"/>
+      <c r="N369" s="6" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="6" t="n"/>
@@ -5074,6 +6581,10 @@
       <c r="H370" s="6" t="n"/>
       <c r="I370" s="6" t="n"/>
       <c r="J370" s="6" t="n"/>
+      <c r="K370" s="6" t="n"/>
+      <c r="L370" s="6" t="n"/>
+      <c r="M370" s="6" t="n"/>
+      <c r="N370" s="6" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="6" t="n"/>
@@ -5086,6 +6597,10 @@
       <c r="H371" s="6" t="n"/>
       <c r="I371" s="6" t="n"/>
       <c r="J371" s="6" t="n"/>
+      <c r="K371" s="6" t="n"/>
+      <c r="L371" s="6" t="n"/>
+      <c r="M371" s="6" t="n"/>
+      <c r="N371" s="6" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="6" t="n"/>
@@ -5098,6 +6613,10 @@
       <c r="H372" s="6" t="n"/>
       <c r="I372" s="6" t="n"/>
       <c r="J372" s="6" t="n"/>
+      <c r="K372" s="6" t="n"/>
+      <c r="L372" s="6" t="n"/>
+      <c r="M372" s="6" t="n"/>
+      <c r="N372" s="6" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="6" t="n"/>
@@ -5110,6 +6629,10 @@
       <c r="H373" s="6" t="n"/>
       <c r="I373" s="6" t="n"/>
       <c r="J373" s="6" t="n"/>
+      <c r="K373" s="6" t="n"/>
+      <c r="L373" s="6" t="n"/>
+      <c r="M373" s="6" t="n"/>
+      <c r="N373" s="6" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="6" t="n"/>
@@ -5122,6 +6645,10 @@
       <c r="H374" s="6" t="n"/>
       <c r="I374" s="6" t="n"/>
       <c r="J374" s="6" t="n"/>
+      <c r="K374" s="6" t="n"/>
+      <c r="L374" s="6" t="n"/>
+      <c r="M374" s="6" t="n"/>
+      <c r="N374" s="6" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="6" t="n"/>
@@ -5134,6 +6661,10 @@
       <c r="H375" s="6" t="n"/>
       <c r="I375" s="6" t="n"/>
       <c r="J375" s="6" t="n"/>
+      <c r="K375" s="6" t="n"/>
+      <c r="L375" s="6" t="n"/>
+      <c r="M375" s="6" t="n"/>
+      <c r="N375" s="6" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="6" t="n"/>
@@ -5146,6 +6677,10 @@
       <c r="H376" s="6" t="n"/>
       <c r="I376" s="6" t="n"/>
       <c r="J376" s="6" t="n"/>
+      <c r="K376" s="6" t="n"/>
+      <c r="L376" s="6" t="n"/>
+      <c r="M376" s="6" t="n"/>
+      <c r="N376" s="6" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="6" t="n"/>
@@ -5158,6 +6693,10 @@
       <c r="H377" s="6" t="n"/>
       <c r="I377" s="6" t="n"/>
       <c r="J377" s="6" t="n"/>
+      <c r="K377" s="6" t="n"/>
+      <c r="L377" s="6" t="n"/>
+      <c r="M377" s="6" t="n"/>
+      <c r="N377" s="6" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="6" t="n"/>
@@ -5170,6 +6709,10 @@
       <c r="H378" s="6" t="n"/>
       <c r="I378" s="6" t="n"/>
       <c r="J378" s="6" t="n"/>
+      <c r="K378" s="6" t="n"/>
+      <c r="L378" s="6" t="n"/>
+      <c r="M378" s="6" t="n"/>
+      <c r="N378" s="6" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="6" t="n"/>
@@ -5182,6 +6725,10 @@
       <c r="H379" s="6" t="n"/>
       <c r="I379" s="6" t="n"/>
       <c r="J379" s="6" t="n"/>
+      <c r="K379" s="6" t="n"/>
+      <c r="L379" s="6" t="n"/>
+      <c r="M379" s="6" t="n"/>
+      <c r="N379" s="6" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="6" t="n"/>
@@ -5194,6 +6741,10 @@
       <c r="H380" s="6" t="n"/>
       <c r="I380" s="6" t="n"/>
       <c r="J380" s="6" t="n"/>
+      <c r="K380" s="6" t="n"/>
+      <c r="L380" s="6" t="n"/>
+      <c r="M380" s="6" t="n"/>
+      <c r="N380" s="6" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="6" t="n"/>
@@ -5206,6 +6757,10 @@
       <c r="H381" s="6" t="n"/>
       <c r="I381" s="6" t="n"/>
       <c r="J381" s="6" t="n"/>
+      <c r="K381" s="6" t="n"/>
+      <c r="L381" s="6" t="n"/>
+      <c r="M381" s="6" t="n"/>
+      <c r="N381" s="6" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="6" t="n"/>
@@ -5218,6 +6773,10 @@
       <c r="H382" s="6" t="n"/>
       <c r="I382" s="6" t="n"/>
       <c r="J382" s="6" t="n"/>
+      <c r="K382" s="6" t="n"/>
+      <c r="L382" s="6" t="n"/>
+      <c r="M382" s="6" t="n"/>
+      <c r="N382" s="6" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="6" t="n"/>
@@ -5230,6 +6789,10 @@
       <c r="H383" s="6" t="n"/>
       <c r="I383" s="6" t="n"/>
       <c r="J383" s="6" t="n"/>
+      <c r="K383" s="6" t="n"/>
+      <c r="L383" s="6" t="n"/>
+      <c r="M383" s="6" t="n"/>
+      <c r="N383" s="6" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="6" t="n"/>
@@ -5242,6 +6805,10 @@
       <c r="H384" s="6" t="n"/>
       <c r="I384" s="6" t="n"/>
       <c r="J384" s="6" t="n"/>
+      <c r="K384" s="6" t="n"/>
+      <c r="L384" s="6" t="n"/>
+      <c r="M384" s="6" t="n"/>
+      <c r="N384" s="6" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="6" t="n"/>
@@ -5254,6 +6821,10 @@
       <c r="H385" s="6" t="n"/>
       <c r="I385" s="6" t="n"/>
       <c r="J385" s="6" t="n"/>
+      <c r="K385" s="6" t="n"/>
+      <c r="L385" s="6" t="n"/>
+      <c r="M385" s="6" t="n"/>
+      <c r="N385" s="6" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="6" t="n"/>
@@ -5266,6 +6837,10 @@
       <c r="H386" s="6" t="n"/>
       <c r="I386" s="6" t="n"/>
       <c r="J386" s="6" t="n"/>
+      <c r="K386" s="6" t="n"/>
+      <c r="L386" s="6" t="n"/>
+      <c r="M386" s="6" t="n"/>
+      <c r="N386" s="6" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="6" t="n"/>
@@ -5278,6 +6853,10 @@
       <c r="H387" s="6" t="n"/>
       <c r="I387" s="6" t="n"/>
       <c r="J387" s="6" t="n"/>
+      <c r="K387" s="6" t="n"/>
+      <c r="L387" s="6" t="n"/>
+      <c r="M387" s="6" t="n"/>
+      <c r="N387" s="6" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="6" t="n"/>
@@ -5290,6 +6869,10 @@
       <c r="H388" s="6" t="n"/>
       <c r="I388" s="6" t="n"/>
       <c r="J388" s="6" t="n"/>
+      <c r="K388" s="6" t="n"/>
+      <c r="L388" s="6" t="n"/>
+      <c r="M388" s="6" t="n"/>
+      <c r="N388" s="6" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="6" t="n"/>
@@ -5302,6 +6885,10 @@
       <c r="H389" s="6" t="n"/>
       <c r="I389" s="6" t="n"/>
       <c r="J389" s="6" t="n"/>
+      <c r="K389" s="6" t="n"/>
+      <c r="L389" s="6" t="n"/>
+      <c r="M389" s="6" t="n"/>
+      <c r="N389" s="6" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="6" t="n"/>
@@ -5314,6 +6901,10 @@
       <c r="H390" s="6" t="n"/>
       <c r="I390" s="6" t="n"/>
       <c r="J390" s="6" t="n"/>
+      <c r="K390" s="6" t="n"/>
+      <c r="L390" s="6" t="n"/>
+      <c r="M390" s="6" t="n"/>
+      <c r="N390" s="6" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="6" t="n"/>
@@ -5326,6 +6917,10 @@
       <c r="H391" s="6" t="n"/>
       <c r="I391" s="6" t="n"/>
       <c r="J391" s="6" t="n"/>
+      <c r="K391" s="6" t="n"/>
+      <c r="L391" s="6" t="n"/>
+      <c r="M391" s="6" t="n"/>
+      <c r="N391" s="6" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="6" t="n"/>
@@ -5338,6 +6933,10 @@
       <c r="H392" s="6" t="n"/>
       <c r="I392" s="6" t="n"/>
       <c r="J392" s="6" t="n"/>
+      <c r="K392" s="6" t="n"/>
+      <c r="L392" s="6" t="n"/>
+      <c r="M392" s="6" t="n"/>
+      <c r="N392" s="6" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="6" t="n"/>
@@ -5350,6 +6949,10 @@
       <c r="H393" s="6" t="n"/>
       <c r="I393" s="6" t="n"/>
       <c r="J393" s="6" t="n"/>
+      <c r="K393" s="6" t="n"/>
+      <c r="L393" s="6" t="n"/>
+      <c r="M393" s="6" t="n"/>
+      <c r="N393" s="6" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="6" t="n"/>
@@ -5362,6 +6965,10 @@
       <c r="H394" s="6" t="n"/>
       <c r="I394" s="6" t="n"/>
       <c r="J394" s="6" t="n"/>
+      <c r="K394" s="6" t="n"/>
+      <c r="L394" s="6" t="n"/>
+      <c r="M394" s="6" t="n"/>
+      <c r="N394" s="6" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="6" t="n"/>
@@ -5374,6 +6981,10 @@
       <c r="H395" s="6" t="n"/>
       <c r="I395" s="6" t="n"/>
       <c r="J395" s="6" t="n"/>
+      <c r="K395" s="6" t="n"/>
+      <c r="L395" s="6" t="n"/>
+      <c r="M395" s="6" t="n"/>
+      <c r="N395" s="6" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="6" t="n"/>
@@ -5386,6 +6997,10 @@
       <c r="H396" s="6" t="n"/>
       <c r="I396" s="6" t="n"/>
       <c r="J396" s="6" t="n"/>
+      <c r="K396" s="6" t="n"/>
+      <c r="L396" s="6" t="n"/>
+      <c r="M396" s="6" t="n"/>
+      <c r="N396" s="6" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="6" t="n"/>
@@ -5398,6 +7013,10 @@
       <c r="H397" s="6" t="n"/>
       <c r="I397" s="6" t="n"/>
       <c r="J397" s="6" t="n"/>
+      <c r="K397" s="6" t="n"/>
+      <c r="L397" s="6" t="n"/>
+      <c r="M397" s="6" t="n"/>
+      <c r="N397" s="6" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="6" t="n"/>
@@ -5410,6 +7029,10 @@
       <c r="H398" s="6" t="n"/>
       <c r="I398" s="6" t="n"/>
       <c r="J398" s="6" t="n"/>
+      <c r="K398" s="6" t="n"/>
+      <c r="L398" s="6" t="n"/>
+      <c r="M398" s="6" t="n"/>
+      <c r="N398" s="6" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="n"/>
@@ -5422,6 +7045,10 @@
       <c r="H399" s="6" t="n"/>
       <c r="I399" s="6" t="n"/>
       <c r="J399" s="6" t="n"/>
+      <c r="K399" s="6" t="n"/>
+      <c r="L399" s="6" t="n"/>
+      <c r="M399" s="6" t="n"/>
+      <c r="N399" s="6" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="6" t="n"/>
@@ -5434,6 +7061,10 @@
       <c r="H400" s="6" t="n"/>
       <c r="I400" s="6" t="n"/>
       <c r="J400" s="6" t="n"/>
+      <c r="K400" s="6" t="n"/>
+      <c r="L400" s="6" t="n"/>
+      <c r="M400" s="6" t="n"/>
+      <c r="N400" s="6" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="6" t="n"/>
@@ -5446,6 +7077,10 @@
       <c r="H401" s="6" t="n"/>
       <c r="I401" s="6" t="n"/>
       <c r="J401" s="6" t="n"/>
+      <c r="K401" s="6" t="n"/>
+      <c r="L401" s="6" t="n"/>
+      <c r="M401" s="6" t="n"/>
+      <c r="N401" s="6" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="6" t="n"/>
@@ -5458,6 +7093,10 @@
       <c r="H402" s="6" t="n"/>
       <c r="I402" s="6" t="n"/>
       <c r="J402" s="6" t="n"/>
+      <c r="K402" s="6" t="n"/>
+      <c r="L402" s="6" t="n"/>
+      <c r="M402" s="6" t="n"/>
+      <c r="N402" s="6" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="6" t="n"/>
@@ -5470,6 +7109,10 @@
       <c r="H403" s="6" t="n"/>
       <c r="I403" s="6" t="n"/>
       <c r="J403" s="6" t="n"/>
+      <c r="K403" s="6" t="n"/>
+      <c r="L403" s="6" t="n"/>
+      <c r="M403" s="6" t="n"/>
+      <c r="N403" s="6" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="6" t="n"/>
@@ -5482,6 +7125,10 @@
       <c r="H404" s="6" t="n"/>
       <c r="I404" s="6" t="n"/>
       <c r="J404" s="6" t="n"/>
+      <c r="K404" s="6" t="n"/>
+      <c r="L404" s="6" t="n"/>
+      <c r="M404" s="6" t="n"/>
+      <c r="N404" s="6" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="6" t="n"/>
@@ -5494,6 +7141,10 @@
       <c r="H405" s="6" t="n"/>
       <c r="I405" s="6" t="n"/>
       <c r="J405" s="6" t="n"/>
+      <c r="K405" s="6" t="n"/>
+      <c r="L405" s="6" t="n"/>
+      <c r="M405" s="6" t="n"/>
+      <c r="N405" s="6" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="6" t="n"/>
@@ -5506,6 +7157,10 @@
       <c r="H406" s="6" t="n"/>
       <c r="I406" s="6" t="n"/>
       <c r="J406" s="6" t="n"/>
+      <c r="K406" s="6" t="n"/>
+      <c r="L406" s="6" t="n"/>
+      <c r="M406" s="6" t="n"/>
+      <c r="N406" s="6" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="6" t="n"/>
@@ -5518,6 +7173,10 @@
       <c r="H407" s="6" t="n"/>
       <c r="I407" s="6" t="n"/>
       <c r="J407" s="6" t="n"/>
+      <c r="K407" s="6" t="n"/>
+      <c r="L407" s="6" t="n"/>
+      <c r="M407" s="6" t="n"/>
+      <c r="N407" s="6" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="6" t="n"/>
@@ -5530,6 +7189,10 @@
       <c r="H408" s="6" t="n"/>
       <c r="I408" s="6" t="n"/>
       <c r="J408" s="6" t="n"/>
+      <c r="K408" s="6" t="n"/>
+      <c r="L408" s="6" t="n"/>
+      <c r="M408" s="6" t="n"/>
+      <c r="N408" s="6" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="6" t="n"/>
@@ -5542,6 +7205,10 @@
       <c r="H409" s="6" t="n"/>
       <c r="I409" s="6" t="n"/>
       <c r="J409" s="6" t="n"/>
+      <c r="K409" s="6" t="n"/>
+      <c r="L409" s="6" t="n"/>
+      <c r="M409" s="6" t="n"/>
+      <c r="N409" s="6" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="6" t="n"/>
@@ -5554,6 +7221,10 @@
       <c r="H410" s="6" t="n"/>
       <c r="I410" s="6" t="n"/>
       <c r="J410" s="6" t="n"/>
+      <c r="K410" s="6" t="n"/>
+      <c r="L410" s="6" t="n"/>
+      <c r="M410" s="6" t="n"/>
+      <c r="N410" s="6" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="6" t="n"/>
@@ -5566,6 +7237,10 @@
       <c r="H411" s="6" t="n"/>
       <c r="I411" s="6" t="n"/>
       <c r="J411" s="6" t="n"/>
+      <c r="K411" s="6" t="n"/>
+      <c r="L411" s="6" t="n"/>
+      <c r="M411" s="6" t="n"/>
+      <c r="N411" s="6" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="6" t="n"/>
@@ -5578,6 +7253,10 @@
       <c r="H412" s="6" t="n"/>
       <c r="I412" s="6" t="n"/>
       <c r="J412" s="6" t="n"/>
+      <c r="K412" s="6" t="n"/>
+      <c r="L412" s="6" t="n"/>
+      <c r="M412" s="6" t="n"/>
+      <c r="N412" s="6" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="6" t="n"/>
@@ -5590,6 +7269,10 @@
       <c r="H413" s="6" t="n"/>
       <c r="I413" s="6" t="n"/>
       <c r="J413" s="6" t="n"/>
+      <c r="K413" s="6" t="n"/>
+      <c r="L413" s="6" t="n"/>
+      <c r="M413" s="6" t="n"/>
+      <c r="N413" s="6" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="6" t="n"/>
@@ -5602,6 +7285,10 @@
       <c r="H414" s="6" t="n"/>
       <c r="I414" s="6" t="n"/>
       <c r="J414" s="6" t="n"/>
+      <c r="K414" s="6" t="n"/>
+      <c r="L414" s="6" t="n"/>
+      <c r="M414" s="6" t="n"/>
+      <c r="N414" s="6" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="6" t="n"/>
@@ -5614,6 +7301,10 @@
       <c r="H415" s="6" t="n"/>
       <c r="I415" s="6" t="n"/>
       <c r="J415" s="6" t="n"/>
+      <c r="K415" s="6" t="n"/>
+      <c r="L415" s="6" t="n"/>
+      <c r="M415" s="6" t="n"/>
+      <c r="N415" s="6" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="6" t="n"/>
@@ -5626,6 +7317,10 @@
       <c r="H416" s="6" t="n"/>
       <c r="I416" s="6" t="n"/>
       <c r="J416" s="6" t="n"/>
+      <c r="K416" s="6" t="n"/>
+      <c r="L416" s="6" t="n"/>
+      <c r="M416" s="6" t="n"/>
+      <c r="N416" s="6" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="6" t="n"/>
@@ -5638,6 +7333,10 @@
       <c r="H417" s="6" t="n"/>
       <c r="I417" s="6" t="n"/>
       <c r="J417" s="6" t="n"/>
+      <c r="K417" s="6" t="n"/>
+      <c r="L417" s="6" t="n"/>
+      <c r="M417" s="6" t="n"/>
+      <c r="N417" s="6" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="6" t="n"/>
@@ -5650,6 +7349,10 @@
       <c r="H418" s="6" t="n"/>
       <c r="I418" s="6" t="n"/>
       <c r="J418" s="6" t="n"/>
+      <c r="K418" s="6" t="n"/>
+      <c r="L418" s="6" t="n"/>
+      <c r="M418" s="6" t="n"/>
+      <c r="N418" s="6" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="6" t="n"/>
@@ -5662,6 +7365,10 @@
       <c r="H419" s="6" t="n"/>
       <c r="I419" s="6" t="n"/>
       <c r="J419" s="6" t="n"/>
+      <c r="K419" s="6" t="n"/>
+      <c r="L419" s="6" t="n"/>
+      <c r="M419" s="6" t="n"/>
+      <c r="N419" s="6" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="6" t="n"/>
@@ -5674,6 +7381,10 @@
       <c r="H420" s="6" t="n"/>
       <c r="I420" s="6" t="n"/>
       <c r="J420" s="6" t="n"/>
+      <c r="K420" s="6" t="n"/>
+      <c r="L420" s="6" t="n"/>
+      <c r="M420" s="6" t="n"/>
+      <c r="N420" s="6" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="6" t="n"/>
@@ -5686,6 +7397,10 @@
       <c r="H421" s="6" t="n"/>
       <c r="I421" s="6" t="n"/>
       <c r="J421" s="6" t="n"/>
+      <c r="K421" s="6" t="n"/>
+      <c r="L421" s="6" t="n"/>
+      <c r="M421" s="6" t="n"/>
+      <c r="N421" s="6" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="6" t="n"/>
@@ -5698,6 +7413,10 @@
       <c r="H422" s="6" t="n"/>
       <c r="I422" s="6" t="n"/>
       <c r="J422" s="6" t="n"/>
+      <c r="K422" s="6" t="n"/>
+      <c r="L422" s="6" t="n"/>
+      <c r="M422" s="6" t="n"/>
+      <c r="N422" s="6" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="6" t="n"/>
@@ -5710,6 +7429,10 @@
       <c r="H423" s="6" t="n"/>
       <c r="I423" s="6" t="n"/>
       <c r="J423" s="6" t="n"/>
+      <c r="K423" s="6" t="n"/>
+      <c r="L423" s="6" t="n"/>
+      <c r="M423" s="6" t="n"/>
+      <c r="N423" s="6" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="6" t="n"/>
@@ -5722,6 +7445,10 @@
       <c r="H424" s="6" t="n"/>
       <c r="I424" s="6" t="n"/>
       <c r="J424" s="6" t="n"/>
+      <c r="K424" s="6" t="n"/>
+      <c r="L424" s="6" t="n"/>
+      <c r="M424" s="6" t="n"/>
+      <c r="N424" s="6" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="6" t="n"/>
@@ -5734,6 +7461,10 @@
       <c r="H425" s="6" t="n"/>
       <c r="I425" s="6" t="n"/>
       <c r="J425" s="6" t="n"/>
+      <c r="K425" s="6" t="n"/>
+      <c r="L425" s="6" t="n"/>
+      <c r="M425" s="6" t="n"/>
+      <c r="N425" s="6" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="6" t="n"/>
@@ -5746,6 +7477,10 @@
       <c r="H426" s="6" t="n"/>
       <c r="I426" s="6" t="n"/>
       <c r="J426" s="6" t="n"/>
+      <c r="K426" s="6" t="n"/>
+      <c r="L426" s="6" t="n"/>
+      <c r="M426" s="6" t="n"/>
+      <c r="N426" s="6" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="6" t="n"/>
@@ -5758,6 +7493,10 @@
       <c r="H427" s="6" t="n"/>
       <c r="I427" s="6" t="n"/>
       <c r="J427" s="6" t="n"/>
+      <c r="K427" s="6" t="n"/>
+      <c r="L427" s="6" t="n"/>
+      <c r="M427" s="6" t="n"/>
+      <c r="N427" s="6" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="6" t="n"/>
@@ -5770,6 +7509,10 @@
       <c r="H428" s="6" t="n"/>
       <c r="I428" s="6" t="n"/>
       <c r="J428" s="6" t="n"/>
+      <c r="K428" s="6" t="n"/>
+      <c r="L428" s="6" t="n"/>
+      <c r="M428" s="6" t="n"/>
+      <c r="N428" s="6" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="6" t="n"/>
@@ -5782,6 +7525,10 @@
       <c r="H429" s="6" t="n"/>
       <c r="I429" s="6" t="n"/>
       <c r="J429" s="6" t="n"/>
+      <c r="K429" s="6" t="n"/>
+      <c r="L429" s="6" t="n"/>
+      <c r="M429" s="6" t="n"/>
+      <c r="N429" s="6" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="6" t="n"/>
@@ -5794,6 +7541,10 @@
       <c r="H430" s="6" t="n"/>
       <c r="I430" s="6" t="n"/>
       <c r="J430" s="6" t="n"/>
+      <c r="K430" s="6" t="n"/>
+      <c r="L430" s="6" t="n"/>
+      <c r="M430" s="6" t="n"/>
+      <c r="N430" s="6" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="6" t="n"/>
@@ -5806,6 +7557,10 @@
       <c r="H431" s="6" t="n"/>
       <c r="I431" s="6" t="n"/>
       <c r="J431" s="6" t="n"/>
+      <c r="K431" s="6" t="n"/>
+      <c r="L431" s="6" t="n"/>
+      <c r="M431" s="6" t="n"/>
+      <c r="N431" s="6" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="6" t="n"/>
@@ -5818,6 +7573,10 @@
       <c r="H432" s="6" t="n"/>
       <c r="I432" s="6" t="n"/>
       <c r="J432" s="6" t="n"/>
+      <c r="K432" s="6" t="n"/>
+      <c r="L432" s="6" t="n"/>
+      <c r="M432" s="6" t="n"/>
+      <c r="N432" s="6" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="6" t="n"/>
@@ -5830,6 +7589,10 @@
       <c r="H433" s="6" t="n"/>
       <c r="I433" s="6" t="n"/>
       <c r="J433" s="6" t="n"/>
+      <c r="K433" s="6" t="n"/>
+      <c r="L433" s="6" t="n"/>
+      <c r="M433" s="6" t="n"/>
+      <c r="N433" s="6" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="6" t="n"/>
@@ -5842,6 +7605,10 @@
       <c r="H434" s="6" t="n"/>
       <c r="I434" s="6" t="n"/>
       <c r="J434" s="6" t="n"/>
+      <c r="K434" s="6" t="n"/>
+      <c r="L434" s="6" t="n"/>
+      <c r="M434" s="6" t="n"/>
+      <c r="N434" s="6" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="6" t="n"/>
@@ -5854,6 +7621,10 @@
       <c r="H435" s="6" t="n"/>
       <c r="I435" s="6" t="n"/>
       <c r="J435" s="6" t="n"/>
+      <c r="K435" s="6" t="n"/>
+      <c r="L435" s="6" t="n"/>
+      <c r="M435" s="6" t="n"/>
+      <c r="N435" s="6" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="6" t="n"/>
@@ -5866,6 +7637,10 @@
       <c r="H436" s="6" t="n"/>
       <c r="I436" s="6" t="n"/>
       <c r="J436" s="6" t="n"/>
+      <c r="K436" s="6" t="n"/>
+      <c r="L436" s="6" t="n"/>
+      <c r="M436" s="6" t="n"/>
+      <c r="N436" s="6" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="6" t="n"/>
@@ -5878,6 +7653,10 @@
       <c r="H437" s="6" t="n"/>
       <c r="I437" s="6" t="n"/>
       <c r="J437" s="6" t="n"/>
+      <c r="K437" s="6" t="n"/>
+      <c r="L437" s="6" t="n"/>
+      <c r="M437" s="6" t="n"/>
+      <c r="N437" s="6" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="6" t="n"/>
@@ -5890,6 +7669,10 @@
       <c r="H438" s="6" t="n"/>
       <c r="I438" s="6" t="n"/>
       <c r="J438" s="6" t="n"/>
+      <c r="K438" s="6" t="n"/>
+      <c r="L438" s="6" t="n"/>
+      <c r="M438" s="6" t="n"/>
+      <c r="N438" s="6" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="6" t="n"/>
@@ -5902,6 +7685,10 @@
       <c r="H439" s="6" t="n"/>
       <c r="I439" s="6" t="n"/>
       <c r="J439" s="6" t="n"/>
+      <c r="K439" s="6" t="n"/>
+      <c r="L439" s="6" t="n"/>
+      <c r="M439" s="6" t="n"/>
+      <c r="N439" s="6" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="6" t="n"/>
@@ -5914,6 +7701,10 @@
       <c r="H440" s="6" t="n"/>
       <c r="I440" s="6" t="n"/>
       <c r="J440" s="6" t="n"/>
+      <c r="K440" s="6" t="n"/>
+      <c r="L440" s="6" t="n"/>
+      <c r="M440" s="6" t="n"/>
+      <c r="N440" s="6" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="6" t="n"/>
@@ -5926,6 +7717,10 @@
       <c r="H441" s="6" t="n"/>
       <c r="I441" s="6" t="n"/>
       <c r="J441" s="6" t="n"/>
+      <c r="K441" s="6" t="n"/>
+      <c r="L441" s="6" t="n"/>
+      <c r="M441" s="6" t="n"/>
+      <c r="N441" s="6" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="6" t="n"/>
@@ -5938,6 +7733,10 @@
       <c r="H442" s="6" t="n"/>
       <c r="I442" s="6" t="n"/>
       <c r="J442" s="6" t="n"/>
+      <c r="K442" s="6" t="n"/>
+      <c r="L442" s="6" t="n"/>
+      <c r="M442" s="6" t="n"/>
+      <c r="N442" s="6" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="6" t="n"/>
@@ -5950,6 +7749,10 @@
       <c r="H443" s="6" t="n"/>
       <c r="I443" s="6" t="n"/>
       <c r="J443" s="6" t="n"/>
+      <c r="K443" s="6" t="n"/>
+      <c r="L443" s="6" t="n"/>
+      <c r="M443" s="6" t="n"/>
+      <c r="N443" s="6" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="6" t="n"/>
@@ -5962,6 +7765,10 @@
       <c r="H444" s="6" t="n"/>
       <c r="I444" s="6" t="n"/>
       <c r="J444" s="6" t="n"/>
+      <c r="K444" s="6" t="n"/>
+      <c r="L444" s="6" t="n"/>
+      <c r="M444" s="6" t="n"/>
+      <c r="N444" s="6" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="6" t="n"/>
@@ -5974,6 +7781,10 @@
       <c r="H445" s="6" t="n"/>
       <c r="I445" s="6" t="n"/>
       <c r="J445" s="6" t="n"/>
+      <c r="K445" s="6" t="n"/>
+      <c r="L445" s="6" t="n"/>
+      <c r="M445" s="6" t="n"/>
+      <c r="N445" s="6" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="6" t="n"/>
@@ -5986,6 +7797,10 @@
       <c r="H446" s="6" t="n"/>
       <c r="I446" s="6" t="n"/>
       <c r="J446" s="6" t="n"/>
+      <c r="K446" s="6" t="n"/>
+      <c r="L446" s="6" t="n"/>
+      <c r="M446" s="6" t="n"/>
+      <c r="N446" s="6" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="6" t="n"/>
@@ -5998,6 +7813,10 @@
       <c r="H447" s="6" t="n"/>
       <c r="I447" s="6" t="n"/>
       <c r="J447" s="6" t="n"/>
+      <c r="K447" s="6" t="n"/>
+      <c r="L447" s="6" t="n"/>
+      <c r="M447" s="6" t="n"/>
+      <c r="N447" s="6" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="6" t="n"/>
@@ -6010,6 +7829,10 @@
       <c r="H448" s="6" t="n"/>
       <c r="I448" s="6" t="n"/>
       <c r="J448" s="6" t="n"/>
+      <c r="K448" s="6" t="n"/>
+      <c r="L448" s="6" t="n"/>
+      <c r="M448" s="6" t="n"/>
+      <c r="N448" s="6" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="6" t="n"/>
@@ -6022,6 +7845,10 @@
       <c r="H449" s="6" t="n"/>
       <c r="I449" s="6" t="n"/>
       <c r="J449" s="6" t="n"/>
+      <c r="K449" s="6" t="n"/>
+      <c r="L449" s="6" t="n"/>
+      <c r="M449" s="6" t="n"/>
+      <c r="N449" s="6" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="6" t="n"/>
@@ -6034,6 +7861,10 @@
       <c r="H450" s="6" t="n"/>
       <c r="I450" s="6" t="n"/>
       <c r="J450" s="6" t="n"/>
+      <c r="K450" s="6" t="n"/>
+      <c r="L450" s="6" t="n"/>
+      <c r="M450" s="6" t="n"/>
+      <c r="N450" s="6" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="6" t="n"/>
@@ -6046,6 +7877,10 @@
       <c r="H451" s="6" t="n"/>
       <c r="I451" s="6" t="n"/>
       <c r="J451" s="6" t="n"/>
+      <c r="K451" s="6" t="n"/>
+      <c r="L451" s="6" t="n"/>
+      <c r="M451" s="6" t="n"/>
+      <c r="N451" s="6" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="6" t="n"/>
@@ -6058,6 +7893,10 @@
       <c r="H452" s="6" t="n"/>
       <c r="I452" s="6" t="n"/>
       <c r="J452" s="6" t="n"/>
+      <c r="K452" s="6" t="n"/>
+      <c r="L452" s="6" t="n"/>
+      <c r="M452" s="6" t="n"/>
+      <c r="N452" s="6" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="6" t="n"/>
@@ -6070,6 +7909,10 @@
       <c r="H453" s="6" t="n"/>
       <c r="I453" s="6" t="n"/>
       <c r="J453" s="6" t="n"/>
+      <c r="K453" s="6" t="n"/>
+      <c r="L453" s="6" t="n"/>
+      <c r="M453" s="6" t="n"/>
+      <c r="N453" s="6" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="6" t="n"/>
@@ -6082,6 +7925,10 @@
       <c r="H454" s="6" t="n"/>
       <c r="I454" s="6" t="n"/>
       <c r="J454" s="6" t="n"/>
+      <c r="K454" s="6" t="n"/>
+      <c r="L454" s="6" t="n"/>
+      <c r="M454" s="6" t="n"/>
+      <c r="N454" s="6" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="6" t="n"/>
@@ -6094,6 +7941,10 @@
       <c r="H455" s="6" t="n"/>
       <c r="I455" s="6" t="n"/>
       <c r="J455" s="6" t="n"/>
+      <c r="K455" s="6" t="n"/>
+      <c r="L455" s="6" t="n"/>
+      <c r="M455" s="6" t="n"/>
+      <c r="N455" s="6" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="6" t="n"/>
@@ -6106,6 +7957,10 @@
       <c r="H456" s="6" t="n"/>
       <c r="I456" s="6" t="n"/>
       <c r="J456" s="6" t="n"/>
+      <c r="K456" s="6" t="n"/>
+      <c r="L456" s="6" t="n"/>
+      <c r="M456" s="6" t="n"/>
+      <c r="N456" s="6" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="6" t="n"/>
@@ -6118,6 +7973,10 @@
       <c r="H457" s="6" t="n"/>
       <c r="I457" s="6" t="n"/>
       <c r="J457" s="6" t="n"/>
+      <c r="K457" s="6" t="n"/>
+      <c r="L457" s="6" t="n"/>
+      <c r="M457" s="6" t="n"/>
+      <c r="N457" s="6" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="6" t="n"/>
@@ -6130,6 +7989,10 @@
       <c r="H458" s="6" t="n"/>
       <c r="I458" s="6" t="n"/>
       <c r="J458" s="6" t="n"/>
+      <c r="K458" s="6" t="n"/>
+      <c r="L458" s="6" t="n"/>
+      <c r="M458" s="6" t="n"/>
+      <c r="N458" s="6" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="6" t="n"/>
@@ -6142,6 +8005,10 @@
       <c r="H459" s="6" t="n"/>
       <c r="I459" s="6" t="n"/>
       <c r="J459" s="6" t="n"/>
+      <c r="K459" s="6" t="n"/>
+      <c r="L459" s="6" t="n"/>
+      <c r="M459" s="6" t="n"/>
+      <c r="N459" s="6" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="6" t="n"/>
@@ -6154,6 +8021,10 @@
       <c r="H460" s="6" t="n"/>
       <c r="I460" s="6" t="n"/>
       <c r="J460" s="6" t="n"/>
+      <c r="K460" s="6" t="n"/>
+      <c r="L460" s="6" t="n"/>
+      <c r="M460" s="6" t="n"/>
+      <c r="N460" s="6" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="6" t="n"/>
@@ -6166,6 +8037,10 @@
       <c r="H461" s="6" t="n"/>
       <c r="I461" s="6" t="n"/>
       <c r="J461" s="6" t="n"/>
+      <c r="K461" s="6" t="n"/>
+      <c r="L461" s="6" t="n"/>
+      <c r="M461" s="6" t="n"/>
+      <c r="N461" s="6" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="6" t="n"/>
@@ -6178,6 +8053,10 @@
       <c r="H462" s="6" t="n"/>
       <c r="I462" s="6" t="n"/>
       <c r="J462" s="6" t="n"/>
+      <c r="K462" s="6" t="n"/>
+      <c r="L462" s="6" t="n"/>
+      <c r="M462" s="6" t="n"/>
+      <c r="N462" s="6" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="6" t="n"/>
@@ -6190,6 +8069,10 @@
       <c r="H463" s="6" t="n"/>
       <c r="I463" s="6" t="n"/>
       <c r="J463" s="6" t="n"/>
+      <c r="K463" s="6" t="n"/>
+      <c r="L463" s="6" t="n"/>
+      <c r="M463" s="6" t="n"/>
+      <c r="N463" s="6" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="6" t="n"/>
@@ -6202,6 +8085,10 @@
       <c r="H464" s="6" t="n"/>
       <c r="I464" s="6" t="n"/>
       <c r="J464" s="6" t="n"/>
+      <c r="K464" s="6" t="n"/>
+      <c r="L464" s="6" t="n"/>
+      <c r="M464" s="6" t="n"/>
+      <c r="N464" s="6" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="6" t="n"/>
@@ -6214,6 +8101,10 @@
       <c r="H465" s="6" t="n"/>
       <c r="I465" s="6" t="n"/>
       <c r="J465" s="6" t="n"/>
+      <c r="K465" s="6" t="n"/>
+      <c r="L465" s="6" t="n"/>
+      <c r="M465" s="6" t="n"/>
+      <c r="N465" s="6" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="6" t="n"/>
@@ -6226,6 +8117,10 @@
       <c r="H466" s="6" t="n"/>
       <c r="I466" s="6" t="n"/>
       <c r="J466" s="6" t="n"/>
+      <c r="K466" s="6" t="n"/>
+      <c r="L466" s="6" t="n"/>
+      <c r="M466" s="6" t="n"/>
+      <c r="N466" s="6" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="6" t="n"/>
@@ -6238,6 +8133,10 @@
       <c r="H467" s="6" t="n"/>
       <c r="I467" s="6" t="n"/>
       <c r="J467" s="6" t="n"/>
+      <c r="K467" s="6" t="n"/>
+      <c r="L467" s="6" t="n"/>
+      <c r="M467" s="6" t="n"/>
+      <c r="N467" s="6" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="6" t="n"/>
@@ -6250,6 +8149,10 @@
       <c r="H468" s="6" t="n"/>
       <c r="I468" s="6" t="n"/>
       <c r="J468" s="6" t="n"/>
+      <c r="K468" s="6" t="n"/>
+      <c r="L468" s="6" t="n"/>
+      <c r="M468" s="6" t="n"/>
+      <c r="N468" s="6" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="6" t="n"/>
@@ -6262,6 +8165,10 @@
       <c r="H469" s="6" t="n"/>
       <c r="I469" s="6" t="n"/>
       <c r="J469" s="6" t="n"/>
+      <c r="K469" s="6" t="n"/>
+      <c r="L469" s="6" t="n"/>
+      <c r="M469" s="6" t="n"/>
+      <c r="N469" s="6" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="6" t="n"/>
@@ -6274,6 +8181,10 @@
       <c r="H470" s="6" t="n"/>
       <c r="I470" s="6" t="n"/>
       <c r="J470" s="6" t="n"/>
+      <c r="K470" s="6" t="n"/>
+      <c r="L470" s="6" t="n"/>
+      <c r="M470" s="6" t="n"/>
+      <c r="N470" s="6" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="6" t="n"/>
@@ -6286,6 +8197,10 @@
       <c r="H471" s="6" t="n"/>
       <c r="I471" s="6" t="n"/>
       <c r="J471" s="6" t="n"/>
+      <c r="K471" s="6" t="n"/>
+      <c r="L471" s="6" t="n"/>
+      <c r="M471" s="6" t="n"/>
+      <c r="N471" s="6" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="6" t="n"/>
@@ -6298,6 +8213,10 @@
       <c r="H472" s="6" t="n"/>
       <c r="I472" s="6" t="n"/>
       <c r="J472" s="6" t="n"/>
+      <c r="K472" s="6" t="n"/>
+      <c r="L472" s="6" t="n"/>
+      <c r="M472" s="6" t="n"/>
+      <c r="N472" s="6" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="6" t="n"/>
@@ -6310,6 +8229,10 @@
       <c r="H473" s="6" t="n"/>
       <c r="I473" s="6" t="n"/>
       <c r="J473" s="6" t="n"/>
+      <c r="K473" s="6" t="n"/>
+      <c r="L473" s="6" t="n"/>
+      <c r="M473" s="6" t="n"/>
+      <c r="N473" s="6" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="6" t="n"/>
@@ -6322,6 +8245,10 @@
       <c r="H474" s="6" t="n"/>
       <c r="I474" s="6" t="n"/>
       <c r="J474" s="6" t="n"/>
+      <c r="K474" s="6" t="n"/>
+      <c r="L474" s="6" t="n"/>
+      <c r="M474" s="6" t="n"/>
+      <c r="N474" s="6" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="6" t="n"/>
@@ -6334,6 +8261,10 @@
       <c r="H475" s="6" t="n"/>
       <c r="I475" s="6" t="n"/>
       <c r="J475" s="6" t="n"/>
+      <c r="K475" s="6" t="n"/>
+      <c r="L475" s="6" t="n"/>
+      <c r="M475" s="6" t="n"/>
+      <c r="N475" s="6" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="6" t="n"/>
@@ -6346,6 +8277,10 @@
       <c r="H476" s="6" t="n"/>
       <c r="I476" s="6" t="n"/>
       <c r="J476" s="6" t="n"/>
+      <c r="K476" s="6" t="n"/>
+      <c r="L476" s="6" t="n"/>
+      <c r="M476" s="6" t="n"/>
+      <c r="N476" s="6" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="6" t="n"/>
@@ -6358,6 +8293,10 @@
       <c r="H477" s="6" t="n"/>
       <c r="I477" s="6" t="n"/>
       <c r="J477" s="6" t="n"/>
+      <c r="K477" s="6" t="n"/>
+      <c r="L477" s="6" t="n"/>
+      <c r="M477" s="6" t="n"/>
+      <c r="N477" s="6" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="6" t="n"/>
@@ -6370,6 +8309,10 @@
       <c r="H478" s="6" t="n"/>
       <c r="I478" s="6" t="n"/>
       <c r="J478" s="6" t="n"/>
+      <c r="K478" s="6" t="n"/>
+      <c r="L478" s="6" t="n"/>
+      <c r="M478" s="6" t="n"/>
+      <c r="N478" s="6" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="6" t="n"/>
@@ -6382,6 +8325,10 @@
       <c r="H479" s="6" t="n"/>
       <c r="I479" s="6" t="n"/>
       <c r="J479" s="6" t="n"/>
+      <c r="K479" s="6" t="n"/>
+      <c r="L479" s="6" t="n"/>
+      <c r="M479" s="6" t="n"/>
+      <c r="N479" s="6" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="6" t="n"/>
@@ -6394,6 +8341,10 @@
       <c r="H480" s="6" t="n"/>
       <c r="I480" s="6" t="n"/>
       <c r="J480" s="6" t="n"/>
+      <c r="K480" s="6" t="n"/>
+      <c r="L480" s="6" t="n"/>
+      <c r="M480" s="6" t="n"/>
+      <c r="N480" s="6" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="6" t="n"/>
@@ -6406,6 +8357,10 @@
       <c r="H481" s="6" t="n"/>
       <c r="I481" s="6" t="n"/>
       <c r="J481" s="6" t="n"/>
+      <c r="K481" s="6" t="n"/>
+      <c r="L481" s="6" t="n"/>
+      <c r="M481" s="6" t="n"/>
+      <c r="N481" s="6" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="6" t="n"/>
@@ -6418,6 +8373,10 @@
       <c r="H482" s="6" t="n"/>
       <c r="I482" s="6" t="n"/>
       <c r="J482" s="6" t="n"/>
+      <c r="K482" s="6" t="n"/>
+      <c r="L482" s="6" t="n"/>
+      <c r="M482" s="6" t="n"/>
+      <c r="N482" s="6" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="6" t="n"/>
@@ -6430,6 +8389,10 @@
       <c r="H483" s="6" t="n"/>
       <c r="I483" s="6" t="n"/>
       <c r="J483" s="6" t="n"/>
+      <c r="K483" s="6" t="n"/>
+      <c r="L483" s="6" t="n"/>
+      <c r="M483" s="6" t="n"/>
+      <c r="N483" s="6" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="6" t="n"/>
@@ -6442,6 +8405,10 @@
       <c r="H484" s="6" t="n"/>
       <c r="I484" s="6" t="n"/>
       <c r="J484" s="6" t="n"/>
+      <c r="K484" s="6" t="n"/>
+      <c r="L484" s="6" t="n"/>
+      <c r="M484" s="6" t="n"/>
+      <c r="N484" s="6" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="6" t="n"/>
@@ -6454,6 +8421,10 @@
       <c r="H485" s="6" t="n"/>
       <c r="I485" s="6" t="n"/>
       <c r="J485" s="6" t="n"/>
+      <c r="K485" s="6" t="n"/>
+      <c r="L485" s="6" t="n"/>
+      <c r="M485" s="6" t="n"/>
+      <c r="N485" s="6" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="6" t="n"/>
@@ -6466,6 +8437,10 @@
       <c r="H486" s="6" t="n"/>
       <c r="I486" s="6" t="n"/>
       <c r="J486" s="6" t="n"/>
+      <c r="K486" s="6" t="n"/>
+      <c r="L486" s="6" t="n"/>
+      <c r="M486" s="6" t="n"/>
+      <c r="N486" s="6" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="6" t="n"/>
@@ -6478,6 +8453,10 @@
       <c r="H487" s="6" t="n"/>
       <c r="I487" s="6" t="n"/>
       <c r="J487" s="6" t="n"/>
+      <c r="K487" s="6" t="n"/>
+      <c r="L487" s="6" t="n"/>
+      <c r="M487" s="6" t="n"/>
+      <c r="N487" s="6" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="6" t="n"/>
@@ -6490,6 +8469,10 @@
       <c r="H488" s="6" t="n"/>
       <c r="I488" s="6" t="n"/>
       <c r="J488" s="6" t="n"/>
+      <c r="K488" s="6" t="n"/>
+      <c r="L488" s="6" t="n"/>
+      <c r="M488" s="6" t="n"/>
+      <c r="N488" s="6" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="6" t="n"/>
@@ -6502,6 +8485,10 @@
       <c r="H489" s="6" t="n"/>
       <c r="I489" s="6" t="n"/>
       <c r="J489" s="6" t="n"/>
+      <c r="K489" s="6" t="n"/>
+      <c r="L489" s="6" t="n"/>
+      <c r="M489" s="6" t="n"/>
+      <c r="N489" s="6" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="6" t="n"/>
@@ -6514,6 +8501,10 @@
       <c r="H490" s="6" t="n"/>
       <c r="I490" s="6" t="n"/>
       <c r="J490" s="6" t="n"/>
+      <c r="K490" s="6" t="n"/>
+      <c r="L490" s="6" t="n"/>
+      <c r="M490" s="6" t="n"/>
+      <c r="N490" s="6" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="6" t="n"/>
@@ -6526,6 +8517,10 @@
       <c r="H491" s="6" t="n"/>
       <c r="I491" s="6" t="n"/>
       <c r="J491" s="6" t="n"/>
+      <c r="K491" s="6" t="n"/>
+      <c r="L491" s="6" t="n"/>
+      <c r="M491" s="6" t="n"/>
+      <c r="N491" s="6" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="6" t="n"/>
@@ -6538,6 +8533,10 @@
       <c r="H492" s="6" t="n"/>
       <c r="I492" s="6" t="n"/>
       <c r="J492" s="6" t="n"/>
+      <c r="K492" s="6" t="n"/>
+      <c r="L492" s="6" t="n"/>
+      <c r="M492" s="6" t="n"/>
+      <c r="N492" s="6" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="6" t="n"/>
@@ -6550,6 +8549,10 @@
       <c r="H493" s="6" t="n"/>
       <c r="I493" s="6" t="n"/>
       <c r="J493" s="6" t="n"/>
+      <c r="K493" s="6" t="n"/>
+      <c r="L493" s="6" t="n"/>
+      <c r="M493" s="6" t="n"/>
+      <c r="N493" s="6" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="6" t="n"/>
@@ -6562,6 +8565,10 @@
       <c r="H494" s="6" t="n"/>
       <c r="I494" s="6" t="n"/>
       <c r="J494" s="6" t="n"/>
+      <c r="K494" s="6" t="n"/>
+      <c r="L494" s="6" t="n"/>
+      <c r="M494" s="6" t="n"/>
+      <c r="N494" s="6" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="6" t="n"/>
@@ -6574,6 +8581,10 @@
       <c r="H495" s="6" t="n"/>
       <c r="I495" s="6" t="n"/>
       <c r="J495" s="6" t="n"/>
+      <c r="K495" s="6" t="n"/>
+      <c r="L495" s="6" t="n"/>
+      <c r="M495" s="6" t="n"/>
+      <c r="N495" s="6" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="6" t="n"/>
@@ -6586,6 +8597,10 @@
       <c r="H496" s="6" t="n"/>
       <c r="I496" s="6" t="n"/>
       <c r="J496" s="6" t="n"/>
+      <c r="K496" s="6" t="n"/>
+      <c r="L496" s="6" t="n"/>
+      <c r="M496" s="6" t="n"/>
+      <c r="N496" s="6" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="6" t="n"/>
@@ -6598,6 +8613,10 @@
       <c r="H497" s="6" t="n"/>
       <c r="I497" s="6" t="n"/>
       <c r="J497" s="6" t="n"/>
+      <c r="K497" s="6" t="n"/>
+      <c r="L497" s="6" t="n"/>
+      <c r="M497" s="6" t="n"/>
+      <c r="N497" s="6" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="6" t="n"/>
@@ -6610,6 +8629,10 @@
       <c r="H498" s="6" t="n"/>
       <c r="I498" s="6" t="n"/>
       <c r="J498" s="6" t="n"/>
+      <c r="K498" s="6" t="n"/>
+      <c r="L498" s="6" t="n"/>
+      <c r="M498" s="6" t="n"/>
+      <c r="N498" s="6" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="6" t="n"/>
@@ -6622,6 +8645,10 @@
       <c r="H499" s="6" t="n"/>
       <c r="I499" s="6" t="n"/>
       <c r="J499" s="6" t="n"/>
+      <c r="K499" s="6" t="n"/>
+      <c r="L499" s="6" t="n"/>
+      <c r="M499" s="6" t="n"/>
+      <c r="N499" s="6" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="6" t="n"/>
@@ -6634,6 +8661,10 @@
       <c r="H500" s="6" t="n"/>
       <c r="I500" s="6" t="n"/>
       <c r="J500" s="6" t="n"/>
+      <c r="K500" s="6" t="n"/>
+      <c r="L500" s="6" t="n"/>
+      <c r="M500" s="6" t="n"/>
+      <c r="N500" s="6" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="6" t="n"/>
@@ -6646,14 +8677,24 @@
       <c r="H501" s="6" t="n"/>
       <c r="I501" s="6" t="n"/>
       <c r="J501" s="6" t="n"/>
+      <c r="K501" s="6" t="n"/>
+      <c r="L501" s="6" t="n"/>
+      <c r="M501" s="6" t="n"/>
+      <c r="N501" s="6" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." type="list">
       <formula1>=Lists!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." type="list">
       <formula1>=Lists!$B$1:$B$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." type="list">
+      <formula1>=Lists!$C$1:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." type="list">
+      <formula1>=Lists!$D$1:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6666,7 +8707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6680,6 +8721,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6692,6 +8743,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6699,6 +8760,23 @@
           <t>Criterion</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
